--- a/data_of_card.xlsx
+++ b/data_of_card.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25831"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\kmutt\compro\Splendor final project\splendor-game\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\GitHub\splendor-game\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{519D8AF6-1771-4064-9A33-050ED99FE729}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AAE499F-A367-445F-8874-792389F357F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{9E734FED-030D-4E04-BF37-A3C9E4A43756}"/>
   </bookViews>
@@ -199,7 +199,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="ปกติ" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -215,7 +215,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="ธีมของ Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -741,7 +741,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B2" s="3">
         <v>2</v>
@@ -821,7 +821,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C6" s="3">
         <v>5</v>

--- a/data_of_card.xlsx
+++ b/data_of_card.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\GitHub\splendor-game\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\kmutt\compro\Splendor final project\splendor-game\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EF0633B-E047-48D9-B7BF-16E362361E54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B758A61-701A-4179-AB03-9D9679D8B9B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="1" xr2:uid="{9E734FED-030D-4E04-BF37-A3C9E4A43756}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{9E734FED-030D-4E04-BF37-A3C9E4A43756}"/>
   </bookViews>
   <sheets>
     <sheet name="dev_card" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="19">
   <si>
     <t>score</t>
   </si>
@@ -80,17 +80,20 @@
   </si>
   <si>
     <t>CostBlack</t>
+  </si>
+  <si>
+    <t>ID</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <charset val="222"/>
       <scheme val="minor"/>
@@ -174,7 +177,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -197,9 +200,10 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="ปกติ" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -215,9 +219,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="ธีมของ Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -255,7 +259,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -361,7 +365,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -503,7 +507,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -511,196 +515,638 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54A96224-6DA4-4492-BCD2-DBFE371CEB0B}">
-  <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <dimension ref="A1:Q91"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="13.8" zeroHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.77734375" style="4"/>
-    <col min="2" max="2" width="8.77734375" style="5"/>
-    <col min="3" max="3" width="10.77734375" style="2" customWidth="1"/>
-    <col min="4" max="8" width="8.77734375" style="3"/>
-    <col min="9" max="16384" width="8.77734375" style="1"/>
+    <col min="1" max="1" width="8.796875" style="8"/>
+    <col min="2" max="2" width="8.796875" style="4"/>
+    <col min="3" max="3" width="8.796875" style="5"/>
+    <col min="4" max="4" width="10.796875" style="2" customWidth="1"/>
+    <col min="5" max="9" width="8.796875" style="3"/>
+    <col min="18" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="C1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="D1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="4">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="8">
         <v>1</v>
       </c>
-      <c r="B2" s="5">
+      <c r="B2" s="4">
+        <v>1</v>
+      </c>
+      <c r="C2" s="5">
         <v>0</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="D2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="3">
-        <v>2</v>
-      </c>
       <c r="E2" s="3">
+        <v>2</v>
+      </c>
+      <c r="F2" s="3">
         <v>1</v>
       </c>
-      <c r="F2" s="3">
+      <c r="G2" s="3">
         <v>5</v>
       </c>
-      <c r="G2" s="3">
+      <c r="H2" s="3">
         <v>6</v>
       </c>
-      <c r="H2" s="3">
+      <c r="I2" s="3">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="4">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="8">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4">
         <v>1</v>
       </c>
-      <c r="B3" s="5">
+      <c r="C3" s="5">
         <v>0</v>
       </c>
-      <c r="C3" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="3">
+      <c r="D3" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="3">
         <v>7</v>
       </c>
-      <c r="E3" s="3">
-        <v>2</v>
-      </c>
       <c r="F3" s="3">
+        <v>2</v>
+      </c>
+      <c r="G3" s="3">
         <v>5</v>
       </c>
-      <c r="G3" s="3">
+      <c r="H3" s="3">
         <v>98</v>
       </c>
-      <c r="H3" s="3">
+      <c r="I3" s="3">
         <v>78</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="4">
-        <v>2</v>
-      </c>
-      <c r="B4" s="5">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="8">
+        <v>3</v>
+      </c>
+      <c r="B4" s="4">
+        <v>2</v>
+      </c>
+      <c r="C4" s="5">
         <v>7</v>
       </c>
-      <c r="C4" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="3">
+      <c r="D4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="3">
         <v>23</v>
       </c>
-      <c r="E4" s="3">
+      <c r="F4" s="3">
         <v>78</v>
       </c>
-      <c r="F4" s="3">
+      <c r="G4" s="3">
         <v>9</v>
       </c>
-      <c r="G4" s="3">
+      <c r="H4" s="3">
         <v>7</v>
       </c>
-      <c r="H4" s="3">
+      <c r="I4" s="3">
         <v>978</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="4">
-        <v>2</v>
-      </c>
-      <c r="B5" s="5">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="8">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4">
+        <v>2</v>
+      </c>
+      <c r="C5" s="5">
         <v>5</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="D5" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="3">
-        <v>3</v>
-      </c>
       <c r="E5" s="3">
         <v>3</v>
       </c>
       <c r="F5" s="3">
+        <v>3</v>
+      </c>
+      <c r="G5" s="3">
         <v>34</v>
       </c>
-      <c r="G5" s="3">
+      <c r="H5" s="3">
         <v>78</v>
       </c>
-      <c r="H5" s="3">
+      <c r="I5" s="3">
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="4">
-        <v>3</v>
-      </c>
-      <c r="B6" s="5">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="8">
+        <v>5</v>
+      </c>
+      <c r="B6" s="4">
+        <v>3</v>
+      </c>
+      <c r="C6" s="5">
         <v>4</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="D6" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="3">
+      <c r="E6" s="3">
         <v>98</v>
       </c>
-      <c r="E6" s="3">
+      <c r="F6" s="3">
         <v>56</v>
-      </c>
-      <c r="F6" s="3">
-        <v>7</v>
       </c>
       <c r="G6" s="3">
         <v>7</v>
       </c>
       <c r="H6" s="3">
+        <v>7</v>
+      </c>
+      <c r="I6" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="4">
-        <v>3</v>
-      </c>
-      <c r="B7" s="5">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="8">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4">
+        <v>3</v>
+      </c>
+      <c r="C7" s="5">
         <v>0</v>
       </c>
-      <c r="C7" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="D7" s="3">
-        <v>3</v>
+      <c r="D7" s="6" t="s">
+        <v>2</v>
       </c>
       <c r="E7" s="3">
+        <v>3</v>
+      </c>
+      <c r="F7" s="3">
         <v>4</v>
       </c>
-      <c r="F7" s="3">
-        <v>2</v>
-      </c>
       <c r="G7" s="3">
+        <v>2</v>
+      </c>
+      <c r="H7" s="3">
         <v>54</v>
       </c>
-      <c r="H7" s="3">
+      <c r="I7" s="3">
         <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="8">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="8">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="8">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="8">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="8">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" s="8">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" s="8">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" s="8">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" s="8">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" s="8">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" s="8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" s="8">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" s="8">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" s="8">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" s="8">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" s="8">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" s="8">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" s="8">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" s="8">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" s="8">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" s="8">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" s="8">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" s="8">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" s="8">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" s="8">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" s="8">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" s="8">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" s="8">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" s="8">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" s="8">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" s="8">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" s="8">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42" s="8">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" s="8">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44" s="8">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45" s="8">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A46" s="8">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A47" s="8">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A48" s="8">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49" s="8">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50" s="8">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A51" s="8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A52" s="8">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A53" s="8">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A54" s="8">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A55" s="8">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A56" s="8">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A57" s="8">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A58" s="8">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A59" s="8">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A60" s="8">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A61" s="8">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A62" s="8">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A63" s="8">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A64" s="8">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A65" s="8">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A66" s="8">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A67" s="8">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A68" s="8">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A69" s="8">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A70" s="8">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A71" s="8">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A72" s="8">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A73" s="8">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A74" s="8">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A75" s="8">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A76" s="8">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A77" s="8">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A78" s="8">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A79" s="8">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A80" s="8">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A81" s="8">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A82" s="8">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A83" s="8">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A84" s="8">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A85" s="8">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A86" s="8">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A87" s="8">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A88" s="8">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A89" s="8">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A90" s="8">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A91" s="8">
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -710,101 +1156,113 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E647C6B-A2D8-48B7-8561-74D848E3342C}">
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="13.8" zeroHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.77734375" style="5"/>
-    <col min="2" max="2" width="8.77734375" style="3" customWidth="1"/>
-    <col min="3" max="6" width="8.77734375" style="3"/>
-    <col min="7" max="16384" width="8.77734375" style="1"/>
+    <col min="1" max="1" width="8.796875" style="8"/>
+    <col min="2" max="2" width="8.796875" style="5"/>
+    <col min="3" max="7" width="8.796875" style="3"/>
+    <col min="8" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="5">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="8">
+        <v>91</v>
+      </c>
+      <c r="B2" s="5">
         <v>5</v>
       </c>
-      <c r="B2" s="3">
-        <v>2</v>
-      </c>
       <c r="C2" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D2" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E2" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F2" s="3">
+        <v>3</v>
+      </c>
+      <c r="G2" s="3">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="5">
-        <v>3</v>
-      </c>
-      <c r="B3" s="3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="8">
+        <v>92</v>
+      </c>
+      <c r="B3" s="5">
+        <v>3</v>
+      </c>
+      <c r="C3" s="3">
         <v>5</v>
       </c>
-      <c r="C3" s="3">
-        <v>3</v>
-      </c>
       <c r="D3" s="3">
+        <v>3</v>
+      </c>
+      <c r="E3" s="3">
         <v>4</v>
       </c>
-      <c r="E3" s="3">
-        <v>2</v>
-      </c>
       <c r="F3" s="3">
+        <v>2</v>
+      </c>
+      <c r="G3" s="3">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="5">
-        <v>3</v>
-      </c>
-      <c r="B4" s="3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="8">
+        <v>93</v>
+      </c>
+      <c r="B4" s="5">
+        <v>3</v>
+      </c>
+      <c r="C4" s="3">
         <v>13</v>
       </c>
-      <c r="C4" s="3">
+      <c r="D4" s="3">
         <v>4</v>
       </c>
-      <c r="D4" s="3">
+      <c r="E4" s="3">
         <v>5</v>
-      </c>
-      <c r="E4" s="3">
-        <v>4</v>
       </c>
       <c r="F4" s="3">
         <v>4</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="5">
-        <v>3</v>
-      </c>
-      <c r="B5" s="3">
-        <v>2</v>
+      <c r="G4" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="8">
+        <v>94</v>
+      </c>
+      <c r="B5" s="5">
+        <v>3</v>
       </c>
       <c r="C5" s="3">
         <v>2</v>
@@ -813,30 +1271,61 @@
         <v>2</v>
       </c>
       <c r="E5" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F5" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="5">
-        <v>3</v>
-      </c>
-      <c r="B6" s="3">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="G5" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="8">
+        <v>95</v>
+      </c>
+      <c r="B6" s="5">
+        <v>3</v>
       </c>
       <c r="C6" s="3">
+        <v>2</v>
+      </c>
+      <c r="D6" s="3">
         <v>5</v>
       </c>
-      <c r="D6" s="3">
+      <c r="E6" s="3">
         <v>4</v>
       </c>
-      <c r="E6" s="3">
-        <v>3</v>
-      </c>
       <c r="F6" s="3">
+        <v>3</v>
+      </c>
+      <c r="G6" s="3">
         <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="8">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="8">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="8">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="8">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="8">
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/data_of_card.xlsx
+++ b/data_of_card.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\kmutt\compro\Splendor final project\splendor-game\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B758A61-701A-4179-AB03-9D9679D8B9B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC722D63-BB54-41EB-B3F6-EF91C7BFD9C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{9E734FED-030D-4E04-BF37-A3C9E4A43756}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9E734FED-030D-4E04-BF37-A3C9E4A43756}"/>
   </bookViews>
   <sheets>
     <sheet name="dev_card" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="19">
   <si>
     <t>score</t>
   </si>
@@ -177,7 +177,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -201,6 +201,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="ปกติ" xfId="0" builtinId="0"/>
@@ -1014,139 +1017,624 @@
         <v>63</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" s="8">
         <v>64</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="8">
         <v>65</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" s="8">
         <v>66</v>
       </c>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" s="8">
         <v>67</v>
       </c>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" s="8">
         <v>68</v>
       </c>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" s="8">
         <v>69</v>
       </c>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" s="8">
         <v>70</v>
       </c>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" s="8">
         <v>71</v>
       </c>
-    </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B72" s="4">
+        <v>3</v>
+      </c>
+      <c r="C72" s="5">
+        <v>5</v>
+      </c>
+      <c r="D72" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E72" s="3">
+        <v>3</v>
+      </c>
+      <c r="F72" s="3">
+        <v>0</v>
+      </c>
+      <c r="G72" s="3">
+        <v>0</v>
+      </c>
+      <c r="H72" s="3">
+        <v>0</v>
+      </c>
+      <c r="I72" s="3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" s="8">
         <v>72</v>
       </c>
-    </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B73" s="4">
+        <v>3</v>
+      </c>
+      <c r="C73" s="5">
+        <v>4</v>
+      </c>
+      <c r="D73" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E73" s="3">
+        <v>0</v>
+      </c>
+      <c r="F73" s="3">
+        <v>0</v>
+      </c>
+      <c r="G73" s="3">
+        <v>0</v>
+      </c>
+      <c r="H73" s="3">
+        <v>0</v>
+      </c>
+      <c r="I73" s="3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" s="8">
         <v>73</v>
       </c>
-    </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B74" s="4">
+        <v>3</v>
+      </c>
+      <c r="C74" s="5">
+        <v>5</v>
+      </c>
+      <c r="D74" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E74" s="3">
+        <v>0</v>
+      </c>
+      <c r="F74" s="3">
+        <v>7</v>
+      </c>
+      <c r="G74" s="3">
+        <v>3</v>
+      </c>
+      <c r="H74" s="3">
+        <v>0</v>
+      </c>
+      <c r="I74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" s="8">
         <v>74</v>
       </c>
-    </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B75" s="4">
+        <v>3</v>
+      </c>
+      <c r="C75" s="5">
+        <v>5</v>
+      </c>
+      <c r="D75" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E75" s="3">
+        <v>7</v>
+      </c>
+      <c r="F75" s="3">
+        <v>3</v>
+      </c>
+      <c r="G75" s="3">
+        <v>0</v>
+      </c>
+      <c r="H75" s="3">
+        <v>0</v>
+      </c>
+      <c r="I75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" s="8">
         <v>75</v>
       </c>
-    </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B76" s="4">
+        <v>3</v>
+      </c>
+      <c r="C76" s="5">
+        <v>4</v>
+      </c>
+      <c r="D76" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E76" s="3">
+        <v>6</v>
+      </c>
+      <c r="F76" s="3">
+        <v>3</v>
+      </c>
+      <c r="G76" s="3">
+        <v>0</v>
+      </c>
+      <c r="H76" s="3">
+        <v>0</v>
+      </c>
+      <c r="I76" s="3">
+        <v>3</v>
+      </c>
+      <c r="K76" s="9"/>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" s="8">
         <v>76</v>
       </c>
-    </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B77" s="4">
+        <v>3</v>
+      </c>
+      <c r="C77" s="5">
+        <v>4</v>
+      </c>
+      <c r="D77" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E77" s="3">
+        <v>3</v>
+      </c>
+      <c r="F77" s="3">
+        <v>0</v>
+      </c>
+      <c r="G77" s="3">
+        <v>0</v>
+      </c>
+      <c r="H77" s="3">
+        <v>3</v>
+      </c>
+      <c r="I77" s="3">
+        <v>6</v>
+      </c>
+      <c r="K77" s="9"/>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" s="8">
         <v>77</v>
       </c>
-    </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B78" s="4">
+        <v>3</v>
+      </c>
+      <c r="C78" s="5">
+        <v>3</v>
+      </c>
+      <c r="D78" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E78" s="3">
+        <v>0</v>
+      </c>
+      <c r="F78" s="3">
+        <v>3</v>
+      </c>
+      <c r="G78" s="3">
+        <v>3</v>
+      </c>
+      <c r="H78" s="3">
+        <v>5</v>
+      </c>
+      <c r="I78" s="3">
+        <v>3</v>
+      </c>
+      <c r="K78" s="9"/>
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" s="8">
         <v>78</v>
       </c>
-    </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B79" s="4">
+        <v>3</v>
+      </c>
+      <c r="C79" s="5">
+        <v>4</v>
+      </c>
+      <c r="D79" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E79" s="3">
+        <v>7</v>
+      </c>
+      <c r="F79" s="3">
+        <v>0</v>
+      </c>
+      <c r="G79" s="3">
+        <v>0</v>
+      </c>
+      <c r="H79" s="3">
+        <v>0</v>
+      </c>
+      <c r="I79" s="3">
+        <v>0</v>
+      </c>
+      <c r="K79" s="9"/>
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" s="8">
         <v>79</v>
       </c>
-    </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B80" s="4">
+        <v>3</v>
+      </c>
+      <c r="C80" s="5">
+        <v>4</v>
+      </c>
+      <c r="D80" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="E80" s="3">
+        <v>0</v>
+      </c>
+      <c r="F80" s="3">
+        <v>0</v>
+      </c>
+      <c r="G80" s="3">
+        <v>7</v>
+      </c>
+      <c r="H80" s="3">
+        <v>0</v>
+      </c>
+      <c r="I80" s="3">
+        <v>0</v>
+      </c>
+      <c r="K80" s="9"/>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" s="8">
         <v>80</v>
       </c>
-    </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B81" s="4">
+        <v>3</v>
+      </c>
+      <c r="C81" s="5">
+        <v>4</v>
+      </c>
+      <c r="D81" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E81" s="3">
+        <v>3</v>
+      </c>
+      <c r="F81" s="3">
+        <v>6</v>
+      </c>
+      <c r="G81" s="3">
+        <v>3</v>
+      </c>
+      <c r="H81" s="3">
+        <v>0</v>
+      </c>
+      <c r="I81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" s="8">
         <v>81</v>
       </c>
-    </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B82" s="4">
+        <v>3</v>
+      </c>
+      <c r="C82" s="5">
+        <v>4</v>
+      </c>
+      <c r="D82" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E82" s="3">
+        <v>0</v>
+      </c>
+      <c r="F82" s="3">
+        <v>0</v>
+      </c>
+      <c r="G82" s="3">
+        <v>0</v>
+      </c>
+      <c r="H82" s="3">
+        <v>7</v>
+      </c>
+      <c r="I82" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" s="8">
         <v>82</v>
       </c>
-    </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B83" s="4">
+        <v>3</v>
+      </c>
+      <c r="C83" s="5">
+        <v>4</v>
+      </c>
+      <c r="D83" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="E83" s="3">
+        <v>0</v>
+      </c>
+      <c r="F83" s="3">
+        <v>3</v>
+      </c>
+      <c r="G83" s="3">
+        <v>6</v>
+      </c>
+      <c r="H83" s="3">
+        <v>3</v>
+      </c>
+      <c r="I83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" s="8">
         <v>83</v>
       </c>
-    </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B84" s="4">
+        <v>3</v>
+      </c>
+      <c r="C84" s="5">
+        <v>3</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E84" s="3">
+        <v>3</v>
+      </c>
+      <c r="F84" s="3">
+        <v>5</v>
+      </c>
+      <c r="G84" s="3">
+        <v>3</v>
+      </c>
+      <c r="H84" s="3">
+        <v>0</v>
+      </c>
+      <c r="I84" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" s="8">
         <v>84</v>
       </c>
-    </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B85" s="4">
+        <v>3</v>
+      </c>
+      <c r="C85" s="5">
+        <v>5</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E85" s="3">
+        <v>0</v>
+      </c>
+      <c r="F85" s="3">
+        <v>0</v>
+      </c>
+      <c r="G85" s="3">
+        <v>0</v>
+      </c>
+      <c r="H85" s="3">
+        <v>7</v>
+      </c>
+      <c r="I85" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" s="8">
         <v>85</v>
       </c>
-    </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B86" s="4">
+        <v>3</v>
+      </c>
+      <c r="C86" s="5">
+        <v>4</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E86" s="3">
+        <v>0</v>
+      </c>
+      <c r="F86" s="3">
+        <v>0</v>
+      </c>
+      <c r="G86" s="3">
+        <v>3</v>
+      </c>
+      <c r="H86" s="3">
+        <v>6</v>
+      </c>
+      <c r="I86" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" s="8">
         <v>86</v>
       </c>
-    </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B87" s="4">
+        <v>3</v>
+      </c>
+      <c r="C87" s="5">
+        <v>4</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E87" s="3">
+        <v>0</v>
+      </c>
+      <c r="F87" s="3">
+        <v>7</v>
+      </c>
+      <c r="G87" s="3">
+        <v>0</v>
+      </c>
+      <c r="H87" s="3">
+        <v>0</v>
+      </c>
+      <c r="I87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" s="8">
         <v>87</v>
       </c>
-    </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B88" s="4">
+        <v>3</v>
+      </c>
+      <c r="C88" s="5">
+        <v>3</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E88" s="3">
+        <v>5</v>
+      </c>
+      <c r="F88" s="3">
+        <v>3</v>
+      </c>
+      <c r="G88" s="3">
+        <v>0</v>
+      </c>
+      <c r="H88" s="3">
+        <v>3</v>
+      </c>
+      <c r="I88" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" s="8">
         <v>88</v>
       </c>
-    </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B89" s="4">
+        <v>3</v>
+      </c>
+      <c r="C89" s="5">
+        <v>3</v>
+      </c>
+      <c r="D89" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E89" s="3">
+        <v>3</v>
+      </c>
+      <c r="F89" s="3">
+        <v>0</v>
+      </c>
+      <c r="G89" s="3">
+        <v>3</v>
+      </c>
+      <c r="H89" s="3">
+        <v>3</v>
+      </c>
+      <c r="I89" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" s="8">
         <v>89</v>
       </c>
-    </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B90" s="4">
+        <v>3</v>
+      </c>
+      <c r="C90" s="5">
+        <v>5</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E90" s="3">
+        <v>0</v>
+      </c>
+      <c r="F90" s="3">
+        <v>0</v>
+      </c>
+      <c r="G90" s="3">
+        <v>7</v>
+      </c>
+      <c r="H90" s="3">
+        <v>3</v>
+      </c>
+      <c r="I90" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" s="8">
         <v>90</v>
+      </c>
+      <c r="B91" s="4">
+        <v>3</v>
+      </c>
+      <c r="C91" s="5">
+        <v>3</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E91" s="3">
+        <v>3</v>
+      </c>
+      <c r="F91" s="3">
+        <v>3</v>
+      </c>
+      <c r="G91" s="3">
+        <v>5</v>
+      </c>
+      <c r="H91" s="3">
+        <v>3</v>
+      </c>
+      <c r="I91" s="3">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data_of_card.xlsx
+++ b/data_of_card.xlsx
@@ -177,7 +177,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -201,9 +201,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="ปกติ" xfId="0" builtinId="0"/>
@@ -1196,7 +1193,7 @@
       <c r="I76" s="3">
         <v>3</v>
       </c>
-      <c r="K76" s="9"/>
+      <c r="K76" s="1"/>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" s="8">
@@ -1226,7 +1223,7 @@
       <c r="I77" s="3">
         <v>6</v>
       </c>
-      <c r="K77" s="9"/>
+      <c r="K77" s="1"/>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" s="8">
@@ -1256,7 +1253,7 @@
       <c r="I78" s="3">
         <v>3</v>
       </c>
-      <c r="K78" s="9"/>
+      <c r="K78" s="1"/>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" s="8">
@@ -1286,7 +1283,7 @@
       <c r="I79" s="3">
         <v>0</v>
       </c>
-      <c r="K79" s="9"/>
+      <c r="K79" s="1"/>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" s="8">
@@ -1316,7 +1313,7 @@
       <c r="I80" s="3">
         <v>0</v>
       </c>
-      <c r="K80" s="9"/>
+      <c r="K80" s="1"/>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" s="8">

--- a/data_of_card.xlsx
+++ b/data_of_card.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\kmutt\compro\Splendor final project\splendor-game\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\GitHub\splendor-game\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B758A61-701A-4179-AB03-9D9679D8B9B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D44EED0-9F16-4BB2-B18C-B2F54C0A9AE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{9E734FED-030D-4E04-BF37-A3C9E4A43756}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{9E734FED-030D-4E04-BF37-A3C9E4A43756}"/>
   </bookViews>
   <sheets>
     <sheet name="dev_card" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="19">
   <si>
     <t>score</t>
   </si>
@@ -89,11 +89,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Tahoma"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="222"/>
       <scheme val="minor"/>
@@ -203,7 +203,7 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="ปกติ" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -219,9 +219,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="ธีมของ Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -259,7 +259,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -365,7 +365,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -507,7 +507,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -516,17 +516,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54A96224-6DA4-4492-BCD2-DBFE371CEB0B}">
   <dimension ref="A1:Q91"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="13.8" zeroHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" zeroHeight="1"/>
   <cols>
-    <col min="1" max="1" width="8.796875" style="8"/>
-    <col min="2" max="2" width="8.796875" style="4"/>
-    <col min="3" max="3" width="8.796875" style="5"/>
-    <col min="4" max="4" width="10.796875" style="2" customWidth="1"/>
-    <col min="5" max="9" width="8.796875" style="3"/>
-    <col min="18" max="16384" width="8.796875" style="1"/>
+    <col min="1" max="1" width="8.77734375" style="8"/>
+    <col min="2" max="2" width="8.77734375" style="4"/>
+    <col min="3" max="3" width="8.77734375" style="5"/>
+    <col min="4" max="4" width="10.77734375" style="2" customWidth="1"/>
+    <col min="5" max="9" width="8.77734375" style="3"/>
+    <col min="18" max="16384" width="8.77734375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9">
       <c r="A1" s="8" t="s">
         <v>18</v>
       </c>
@@ -555,7 +555,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9">
       <c r="A2" s="8">
         <v>1</v>
       </c>
@@ -566,25 +566,25 @@
         <v>0</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H2" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I2" s="3">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="8">
         <v>2</v>
       </c>
@@ -598,553 +598,889 @@
         <v>2</v>
       </c>
       <c r="E3" s="3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F3" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G3" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H3" s="3">
-        <v>98</v>
+        <v>2</v>
       </c>
       <c r="I3" s="3">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="8">
         <v>3</v>
       </c>
       <c r="B4" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C4" s="5">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E4" s="3">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="F4" s="3">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="G4" s="3">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H4" s="3">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I4" s="3">
-        <v>978</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" s="8">
         <v>4</v>
       </c>
       <c r="B5" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5" s="5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E5" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F5" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G5" s="3">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="H5" s="3">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="I5" s="3">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" s="8">
         <v>5</v>
       </c>
       <c r="B6" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C6" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E6" s="3">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="F6" s="3">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="G6" s="3">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H6" s="3">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I6" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" s="8">
         <v>6</v>
       </c>
       <c r="B7" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C7" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E7" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F7" s="3">
+        <v>0</v>
+      </c>
+      <c r="G7" s="3">
         <v>4</v>
       </c>
-      <c r="G7" s="3">
-        <v>2</v>
-      </c>
       <c r="H7" s="3">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="I7" s="3">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8" s="8">
         <v>7</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B8" s="4">
+        <v>1</v>
+      </c>
+      <c r="C8" s="5">
+        <v>0</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3">
+        <v>1</v>
+      </c>
+      <c r="H8" s="3">
+        <v>3</v>
+      </c>
+      <c r="I8" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="8">
         <v>8</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B9" s="4">
+        <v>1</v>
+      </c>
+      <c r="C9" s="5">
+        <v>0</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E9" s="3">
+        <v>1</v>
+      </c>
+      <c r="F9" s="3">
+        <v>1</v>
+      </c>
+      <c r="G9" s="3">
+        <v>1</v>
+      </c>
+      <c r="H9" s="3">
+        <v>1</v>
+      </c>
+      <c r="I9" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" s="8">
         <v>9</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B10" s="4">
+        <v>1</v>
+      </c>
+      <c r="C10" s="5">
+        <v>0</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E10" s="3">
+        <v>1</v>
+      </c>
+      <c r="F10" s="3">
+        <v>2</v>
+      </c>
+      <c r="G10" s="3">
+        <v>1</v>
+      </c>
+      <c r="H10" s="3">
+        <v>1</v>
+      </c>
+      <c r="I10" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" s="8">
         <v>10</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B11" s="4">
+        <v>1</v>
+      </c>
+      <c r="C11" s="5">
+        <v>1</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E11" s="3">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3">
+        <v>4</v>
+      </c>
+      <c r="G11" s="3">
+        <v>0</v>
+      </c>
+      <c r="H11" s="3">
+        <v>0</v>
+      </c>
+      <c r="I11" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" s="8">
         <v>11</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B12" s="4">
+        <v>1</v>
+      </c>
+      <c r="C12" s="5">
+        <v>0</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E12" s="3">
+        <v>2</v>
+      </c>
+      <c r="F12" s="3">
+        <v>1</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0</v>
+      </c>
+      <c r="H12" s="3">
+        <v>0</v>
+      </c>
+      <c r="I12" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13" s="8">
         <v>12</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B13" s="4">
+        <v>1</v>
+      </c>
+      <c r="C13" s="5">
+        <v>0</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E13" s="3">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3">
+        <v>1</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0</v>
+      </c>
+      <c r="H13" s="3">
+        <v>2</v>
+      </c>
+      <c r="I13" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
       <c r="A14" s="8">
         <v>13</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B14" s="4">
+        <v>1</v>
+      </c>
+      <c r="C14" s="5">
+        <v>0</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
+        <v>2</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
+        <v>2</v>
+      </c>
+      <c r="I14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
       <c r="A15" s="8">
         <v>14</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B15" s="4">
+        <v>1</v>
+      </c>
+      <c r="C15" s="5">
+        <v>0</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E15" s="3">
+        <v>1</v>
+      </c>
+      <c r="F15" s="3">
+        <v>0</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="3">
+        <v>0</v>
+      </c>
+      <c r="I15" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
       <c r="A16" s="8">
         <v>15</v>
       </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B16" s="4">
+        <v>1</v>
+      </c>
+      <c r="C16" s="5">
+        <v>0</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E16" s="3">
+        <v>0</v>
+      </c>
+      <c r="F16" s="3">
+        <v>0</v>
+      </c>
+      <c r="G16" s="3">
+        <v>0</v>
+      </c>
+      <c r="H16" s="3">
+        <v>0</v>
+      </c>
+      <c r="I16" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
       <c r="A17" s="8">
         <v>16</v>
       </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B17" s="4">
+        <v>1</v>
+      </c>
+      <c r="C17" s="5">
+        <v>0</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E17" s="3">
+        <v>1</v>
+      </c>
+      <c r="F17" s="3">
+        <v>1</v>
+      </c>
+      <c r="G17" s="3">
+        <v>0</v>
+      </c>
+      <c r="H17" s="3">
+        <v>1</v>
+      </c>
+      <c r="I17" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
       <c r="A18" s="8">
         <v>17</v>
       </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B18" s="4">
+        <v>1</v>
+      </c>
+      <c r="C18" s="5">
+        <v>0</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E18" s="3">
+        <v>0</v>
+      </c>
+      <c r="F18" s="3">
+        <v>2</v>
+      </c>
+      <c r="G18" s="3">
+        <v>0</v>
+      </c>
+      <c r="H18" s="3">
+        <v>0</v>
+      </c>
+      <c r="I18" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
       <c r="A19" s="8">
         <v>18</v>
       </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B19" s="4">
+        <v>1</v>
+      </c>
+      <c r="C19" s="5">
+        <v>0</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E19" s="3">
+        <v>0</v>
+      </c>
+      <c r="F19" s="3">
+        <v>2</v>
+      </c>
+      <c r="G19" s="3">
+        <v>2</v>
+      </c>
+      <c r="H19" s="3">
+        <v>0</v>
+      </c>
+      <c r="I19" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
       <c r="A20" s="8">
         <v>19</v>
       </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B20" s="4">
+        <v>1</v>
+      </c>
+      <c r="C20" s="5">
+        <v>0</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
+        <v>3</v>
+      </c>
+      <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
       <c r="A21" s="8">
         <v>20</v>
       </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B21" s="4">
+        <v>1</v>
+      </c>
+      <c r="C21" s="5">
+        <v>0</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E21" s="3">
+        <v>1</v>
+      </c>
+      <c r="F21" s="3">
+        <v>1</v>
+      </c>
+      <c r="G21" s="3">
+        <v>0</v>
+      </c>
+      <c r="H21" s="3">
+        <v>1</v>
+      </c>
+      <c r="I21" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
       <c r="A22" s="8">
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9">
       <c r="A23" s="8">
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9">
       <c r="A24" s="8">
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9">
       <c r="A25" s="8">
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9">
       <c r="A26" s="8">
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9">
       <c r="A27" s="8">
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9">
       <c r="A28" s="8">
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9">
       <c r="A29" s="8">
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9">
       <c r="A30" s="8">
         <v>29</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9">
       <c r="A31" s="8">
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9">
       <c r="A32" s="8">
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:1">
       <c r="A33" s="8">
         <v>32</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:1">
       <c r="A34" s="8">
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:1">
       <c r="A35" s="8">
         <v>34</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:1">
       <c r="A36" s="8">
         <v>35</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:1">
       <c r="A37" s="8">
         <v>36</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:1">
       <c r="A38" s="8">
         <v>37</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:1">
       <c r="A39" s="8">
         <v>38</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:1">
       <c r="A40" s="8">
         <v>39</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:1">
       <c r="A41" s="8">
         <v>40</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:1">
       <c r="A42" s="8">
         <v>41</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:1">
       <c r="A43" s="8">
         <v>42</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:1">
       <c r="A44" s="8">
         <v>43</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:1">
       <c r="A45" s="8">
         <v>44</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:1">
       <c r="A46" s="8">
         <v>45</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:1">
       <c r="A47" s="8">
         <v>46</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:1">
       <c r="A48" s="8">
         <v>47</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:1">
       <c r="A49" s="8">
         <v>48</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:1">
       <c r="A50" s="8">
         <v>49</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:1">
       <c r="A51" s="8">
         <v>50</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:1">
       <c r="A52" s="8">
         <v>51</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:1">
       <c r="A53" s="8">
         <v>52</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:1">
       <c r="A54" s="8">
         <v>53</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:1">
       <c r="A55" s="8">
         <v>54</v>
       </c>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:1">
       <c r="A56" s="8">
         <v>55</v>
       </c>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:1">
       <c r="A57" s="8">
         <v>56</v>
       </c>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:1">
       <c r="A58" s="8">
         <v>57</v>
       </c>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:1">
       <c r="A59" s="8">
         <v>58</v>
       </c>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:1">
       <c r="A60" s="8">
         <v>59</v>
       </c>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:1">
       <c r="A61" s="8">
         <v>60</v>
       </c>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:1">
       <c r="A62" s="8">
         <v>61</v>
       </c>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:1">
       <c r="A63" s="8">
         <v>62</v>
       </c>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:1">
       <c r="A64" s="8">
         <v>63</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:1">
       <c r="A65" s="8">
         <v>64</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:1">
       <c r="A66" s="8">
         <v>65</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:1">
       <c r="A67" s="8">
         <v>66</v>
       </c>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:1">
       <c r="A68" s="8">
         <v>67</v>
       </c>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:1">
       <c r="A69" s="8">
         <v>68</v>
       </c>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:1">
       <c r="A70" s="8">
         <v>69</v>
       </c>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:1">
       <c r="A71" s="8">
         <v>70</v>
       </c>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:1">
       <c r="A72" s="8">
         <v>71</v>
       </c>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:1">
       <c r="A73" s="8">
         <v>72</v>
       </c>
     </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:1">
       <c r="A74" s="8">
         <v>73</v>
       </c>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:1">
       <c r="A75" s="8">
         <v>74</v>
       </c>
     </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:1">
       <c r="A76" s="8">
         <v>75</v>
       </c>
     </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:1">
       <c r="A77" s="8">
         <v>76</v>
       </c>
     </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:1">
       <c r="A78" s="8">
         <v>77</v>
       </c>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:1">
       <c r="A79" s="8">
         <v>78</v>
       </c>
     </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:1">
       <c r="A80" s="8">
         <v>79</v>
       </c>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:1">
       <c r="A81" s="8">
         <v>80</v>
       </c>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:1">
       <c r="A82" s="8">
         <v>81</v>
       </c>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:1">
       <c r="A83" s="8">
         <v>82</v>
       </c>
     </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:1">
       <c r="A84" s="8">
         <v>83</v>
       </c>
     </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:1">
       <c r="A85" s="8">
         <v>84</v>
       </c>
     </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:1">
       <c r="A86" s="8">
         <v>85</v>
       </c>
     </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:1">
       <c r="A87" s="8">
         <v>86</v>
       </c>
     </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:1">
       <c r="A88" s="8">
         <v>87</v>
       </c>
     </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:1">
       <c r="A89" s="8">
         <v>88</v>
       </c>
     </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:1">
       <c r="A90" s="8">
         <v>89</v>
       </c>
     </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:1">
       <c r="A91" s="8">
         <v>90</v>
       </c>
@@ -1157,15 +1493,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E647C6B-A2D8-48B7-8561-74D848E3342C}">
   <dimension ref="A1:G11"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="13.8" zeroHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" zeroHeight="1"/>
   <cols>
-    <col min="1" max="1" width="8.796875" style="8"/>
-    <col min="2" max="2" width="8.796875" style="5"/>
-    <col min="3" max="7" width="8.796875" style="3"/>
-    <col min="8" max="16384" width="8.796875" style="1"/>
+    <col min="1" max="1" width="8.77734375" style="8"/>
+    <col min="2" max="2" width="8.77734375" style="5"/>
+    <col min="3" max="7" width="8.77734375" style="3"/>
+    <col min="8" max="16384" width="8.77734375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7">
       <c r="A1" s="8" t="s">
         <v>18</v>
       </c>
@@ -1188,7 +1524,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7">
       <c r="A2" s="8">
         <v>91</v>
       </c>
@@ -1211,7 +1547,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7">
       <c r="A3" s="8">
         <v>92</v>
       </c>
@@ -1234,7 +1570,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7">
       <c r="A4" s="8">
         <v>93</v>
       </c>
@@ -1257,7 +1593,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7">
       <c r="A5" s="8">
         <v>94</v>
       </c>
@@ -1280,7 +1616,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7">
       <c r="A6" s="8">
         <v>95</v>
       </c>
@@ -1303,27 +1639,27 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7">
       <c r="A7" s="8">
         <v>96</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7">
       <c r="A8" s="8">
         <v>97</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7">
       <c r="A9" s="8">
         <v>98</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7">
       <c r="A10" s="8">
         <v>99</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7">
       <c r="A11" s="8">
         <v>100</v>
       </c>

--- a/data_of_card.xlsx
+++ b/data_of_card.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\kmutt\compro\Splendor final project\splendor-game\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\GitHub\splendor-game\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC722D63-BB54-41EB-B3F6-EF91C7BFD9C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{457B7B8F-B9D5-480F-942D-1767F7F18A27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9E734FED-030D-4E04-BF37-A3C9E4A43756}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{9E734FED-030D-4E04-BF37-A3C9E4A43756}"/>
   </bookViews>
   <sheets>
     <sheet name="dev_card" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="19">
   <si>
     <t>score</t>
   </si>
@@ -89,11 +89,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Tahoma"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="222"/>
       <scheme val="minor"/>
@@ -203,7 +203,7 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="ปกติ" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -219,9 +219,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="ธีมของ Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -259,7 +259,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -365,7 +365,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -507,7 +507,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -516,17 +516,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54A96224-6DA4-4492-BCD2-DBFE371CEB0B}">
   <dimension ref="A1:Q91"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="13.8" zeroHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" zeroHeight="1"/>
   <cols>
-    <col min="1" max="1" width="8.796875" style="8"/>
-    <col min="2" max="2" width="8.796875" style="4"/>
-    <col min="3" max="3" width="8.796875" style="5"/>
-    <col min="4" max="4" width="10.796875" style="2" customWidth="1"/>
-    <col min="5" max="9" width="8.796875" style="3"/>
-    <col min="18" max="16384" width="8.796875" style="1"/>
+    <col min="1" max="1" width="8.77734375" style="8"/>
+    <col min="2" max="2" width="8.77734375" style="4"/>
+    <col min="3" max="3" width="8.77734375" style="5"/>
+    <col min="4" max="4" width="10.77734375" style="2" customWidth="1"/>
+    <col min="5" max="9" width="8.77734375" style="3"/>
+    <col min="18" max="16384" width="8.77734375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9">
       <c r="A1" s="8" t="s">
         <v>18</v>
       </c>
@@ -555,7 +555,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9">
       <c r="A2" s="8">
         <v>1</v>
       </c>
@@ -563,28 +563,28 @@
         <v>1</v>
       </c>
       <c r="C2" s="5">
-        <v>0</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="E2" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F2" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G2" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H2" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I2" s="3">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="8">
         <v>2</v>
       </c>
@@ -594,462 +594,582 @@
       <c r="C3" s="5">
         <v>0</v>
       </c>
-      <c r="D3" s="6" t="s">
-        <v>2</v>
+      <c r="D3" s="2" t="s">
+        <v>3</v>
       </c>
       <c r="E3" s="3">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F3" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G3" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H3" s="3">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="I3" s="3">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="8">
         <v>3</v>
       </c>
       <c r="B4" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C4" s="5">
-        <v>7</v>
-      </c>
-      <c r="D4" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>3</v>
       </c>
       <c r="E4" s="3">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="F4" s="3">
-        <v>78</v>
+        <v>1</v>
       </c>
       <c r="G4" s="3">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H4" s="3">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I4" s="3">
-        <v>978</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" s="8">
         <v>4</v>
       </c>
       <c r="B5" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5" s="5">
-        <v>5</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>5</v>
+        <v>0</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>3</v>
       </c>
       <c r="E5" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F5" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G5" s="3">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="H5" s="3">
-        <v>78</v>
+        <v>2</v>
       </c>
       <c r="I5" s="3">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" s="8">
         <v>5</v>
       </c>
       <c r="B6" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C6" s="5">
-        <v>4</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>2</v>
       </c>
       <c r="E6" s="3">
-        <v>98</v>
+        <v>1</v>
       </c>
       <c r="F6" s="3">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="G6" s="3">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H6" s="3">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I6" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" s="8">
         <v>6</v>
       </c>
       <c r="B7" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C7" s="5">
         <v>0</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E7" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F7" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G7" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H7" s="3">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="I7" s="3">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8" s="8">
         <v>7</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B8" s="4">
+        <v>1</v>
+      </c>
+      <c r="C8" s="5">
+        <v>0</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E8" s="3">
+        <v>1</v>
+      </c>
+      <c r="F8" s="3">
+        <v>1</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="3">
+        <v>1</v>
+      </c>
+      <c r="I8" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="8">
         <v>8</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B9" s="4">
+        <v>1</v>
+      </c>
+      <c r="C9" s="5">
+        <v>0</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3">
+        <v>2</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0</v>
+      </c>
+      <c r="H9" s="3">
+        <v>0</v>
+      </c>
+      <c r="I9" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" s="8">
         <v>9</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B10" s="4">
+        <v>1</v>
+      </c>
+      <c r="C10" s="5">
+        <v>0</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3">
+        <v>2</v>
+      </c>
+      <c r="G10" s="3">
+        <v>2</v>
+      </c>
+      <c r="H10" s="3">
+        <v>0</v>
+      </c>
+      <c r="I10" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" s="8">
         <v>10</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B11" s="4">
+        <v>1</v>
+      </c>
+      <c r="C11" s="5">
+        <v>0</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E11" s="3">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3">
+        <v>3</v>
+      </c>
+      <c r="G11" s="3">
+        <v>0</v>
+      </c>
+      <c r="H11" s="3">
+        <v>0</v>
+      </c>
+      <c r="I11" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" s="8">
         <v>11</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B12" s="4">
+        <v>1</v>
+      </c>
+      <c r="C12" s="5">
+        <v>0</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E12" s="3">
+        <v>1</v>
+      </c>
+      <c r="F12" s="3">
+        <v>1</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0</v>
+      </c>
+      <c r="H12" s="3">
+        <v>1</v>
+      </c>
+      <c r="I12" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13" s="8">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9">
       <c r="A14" s="8">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9">
       <c r="A15" s="8">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9">
       <c r="A16" s="8">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1">
       <c r="A17" s="8">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1">
       <c r="A18" s="8">
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1">
       <c r="A19" s="8">
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1">
       <c r="A20" s="8">
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1">
       <c r="A21" s="8">
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1">
       <c r="A22" s="8">
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1">
       <c r="A23" s="8">
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1">
       <c r="A24" s="8">
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1">
       <c r="A25" s="8">
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1">
       <c r="A26" s="8">
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:1">
       <c r="A27" s="8">
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1">
       <c r="A28" s="8">
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:1">
       <c r="A29" s="8">
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:1">
       <c r="A30" s="8">
         <v>29</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:1">
       <c r="A31" s="8">
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:1">
       <c r="A32" s="8">
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:1">
       <c r="A33" s="8">
         <v>32</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:1">
       <c r="A34" s="8">
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:1">
       <c r="A35" s="8">
         <v>34</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:1">
       <c r="A36" s="8">
         <v>35</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:1">
       <c r="A37" s="8">
         <v>36</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:1">
       <c r="A38" s="8">
         <v>37</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:1">
       <c r="A39" s="8">
         <v>38</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:1">
       <c r="A40" s="8">
         <v>39</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:1">
       <c r="A41" s="8">
         <v>40</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:1">
       <c r="A42" s="8">
         <v>41</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:1">
       <c r="A43" s="8">
         <v>42</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:1">
       <c r="A44" s="8">
         <v>43</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:1">
       <c r="A45" s="8">
         <v>44</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:1">
       <c r="A46" s="8">
         <v>45</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:1">
       <c r="A47" s="8">
         <v>46</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:1">
       <c r="A48" s="8">
         <v>47</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:1">
       <c r="A49" s="8">
         <v>48</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:1">
       <c r="A50" s="8">
         <v>49</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:1">
       <c r="A51" s="8">
         <v>50</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:1">
       <c r="A52" s="8">
         <v>51</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:1">
       <c r="A53" s="8">
         <v>52</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:1">
       <c r="A54" s="8">
         <v>53</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:1">
       <c r="A55" s="8">
         <v>54</v>
       </c>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:1">
       <c r="A56" s="8">
         <v>55</v>
       </c>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:1">
       <c r="A57" s="8">
         <v>56</v>
       </c>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:1">
       <c r="A58" s="8">
         <v>57</v>
       </c>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:1">
       <c r="A59" s="8">
         <v>58</v>
       </c>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:1">
       <c r="A60" s="8">
         <v>59</v>
       </c>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:1">
       <c r="A61" s="8">
         <v>60</v>
       </c>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:1">
       <c r="A62" s="8">
         <v>61</v>
       </c>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:1">
       <c r="A63" s="8">
         <v>62</v>
       </c>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:1">
       <c r="A64" s="8">
         <v>63</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:11">
       <c r="A65" s="8">
         <v>64</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:11">
       <c r="A66" s="8">
         <v>65</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:11">
       <c r="A67" s="8">
         <v>66</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:11">
       <c r="A68" s="8">
         <v>67</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:11">
       <c r="A69" s="8">
         <v>68</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:11">
       <c r="A70" s="8">
         <v>69</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:11">
       <c r="A71" s="8">
         <v>70</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:11">
       <c r="A72" s="8">
         <v>71</v>
       </c>
@@ -1078,7 +1198,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:11">
       <c r="A73" s="8">
         <v>72</v>
       </c>
@@ -1107,7 +1227,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:11">
       <c r="A74" s="8">
         <v>73</v>
       </c>
@@ -1136,7 +1256,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:11">
       <c r="A75" s="8">
         <v>74</v>
       </c>
@@ -1165,7 +1285,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:11">
       <c r="A76" s="8">
         <v>75</v>
       </c>
@@ -1195,7 +1315,7 @@
       </c>
       <c r="K76" s="1"/>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:11">
       <c r="A77" s="8">
         <v>76</v>
       </c>
@@ -1225,7 +1345,7 @@
       </c>
       <c r="K77" s="1"/>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:11">
       <c r="A78" s="8">
         <v>77</v>
       </c>
@@ -1255,7 +1375,7 @@
       </c>
       <c r="K78" s="1"/>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:11">
       <c r="A79" s="8">
         <v>78</v>
       </c>
@@ -1285,7 +1405,7 @@
       </c>
       <c r="K79" s="1"/>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:11">
       <c r="A80" s="8">
         <v>79</v>
       </c>
@@ -1315,7 +1435,7 @@
       </c>
       <c r="K80" s="1"/>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9">
       <c r="A81" s="8">
         <v>80</v>
       </c>
@@ -1344,7 +1464,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9">
       <c r="A82" s="8">
         <v>81</v>
       </c>
@@ -1373,7 +1493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9">
       <c r="A83" s="8">
         <v>82</v>
       </c>
@@ -1402,7 +1522,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9">
       <c r="A84" s="8">
         <v>83</v>
       </c>
@@ -1431,7 +1551,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9">
       <c r="A85" s="8">
         <v>84</v>
       </c>
@@ -1460,7 +1580,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9">
       <c r="A86" s="8">
         <v>85</v>
       </c>
@@ -1489,7 +1609,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9">
       <c r="A87" s="8">
         <v>86</v>
       </c>
@@ -1518,7 +1638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9">
       <c r="A88" s="8">
         <v>87</v>
       </c>
@@ -1547,7 +1667,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9">
       <c r="A89" s="8">
         <v>88</v>
       </c>
@@ -1576,7 +1696,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9">
       <c r="A90" s="8">
         <v>89</v>
       </c>
@@ -1605,7 +1725,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9">
       <c r="A91" s="8">
         <v>90</v>
       </c>
@@ -1642,15 +1762,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E647C6B-A2D8-48B7-8561-74D848E3342C}">
   <dimension ref="A1:G11"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="13.8" zeroHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" zeroHeight="1"/>
   <cols>
-    <col min="1" max="1" width="8.796875" style="8"/>
-    <col min="2" max="2" width="8.796875" style="5"/>
-    <col min="3" max="7" width="8.796875" style="3"/>
-    <col min="8" max="16384" width="8.796875" style="1"/>
+    <col min="1" max="1" width="8.77734375" style="8"/>
+    <col min="2" max="2" width="8.77734375" style="5"/>
+    <col min="3" max="7" width="8.77734375" style="3"/>
+    <col min="8" max="16384" width="8.77734375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7">
       <c r="A1" s="8" t="s">
         <v>18</v>
       </c>
@@ -1673,7 +1793,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7">
       <c r="A2" s="8">
         <v>91</v>
       </c>
@@ -1696,7 +1816,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7">
       <c r="A3" s="8">
         <v>92</v>
       </c>
@@ -1719,7 +1839,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7">
       <c r="A4" s="8">
         <v>93</v>
       </c>
@@ -1742,7 +1862,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7">
       <c r="A5" s="8">
         <v>94</v>
       </c>
@@ -1765,7 +1885,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7">
       <c r="A6" s="8">
         <v>95</v>
       </c>
@@ -1788,27 +1908,27 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7">
       <c r="A7" s="8">
         <v>96</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7">
       <c r="A8" s="8">
         <v>97</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7">
       <c r="A9" s="8">
         <v>98</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7">
       <c r="A10" s="8">
         <v>99</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7">
       <c r="A11" s="8">
         <v>100</v>
       </c>

--- a/data_of_card.xlsx
+++ b/data_of_card.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\GitHub\splendor-game\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{457B7B8F-B9D5-480F-942D-1767F7F18A27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB385A1A-A7C2-404E-9A61-307FE578BAD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{9E734FED-030D-4E04-BF37-A3C9E4A43756}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="19">
   <si>
     <t>score</t>
   </si>
@@ -563,25 +563,25 @@
         <v>1</v>
       </c>
       <c r="C2" s="5">
-        <v>1</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>5</v>
+        <v>0</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>2</v>
       </c>
       <c r="E2" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G2" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I2" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -594,20 +594,20 @@
       <c r="C3" s="5">
         <v>0</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>3</v>
+      <c r="D3" s="6" t="s">
+        <v>2</v>
       </c>
       <c r="E3" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H3" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I3" s="3">
         <v>0</v>
@@ -623,14 +623,14 @@
       <c r="C4" s="5">
         <v>0</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>3</v>
+      <c r="D4" s="6" t="s">
+        <v>4</v>
       </c>
       <c r="E4" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F4" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4" s="3">
         <v>0</v>
@@ -639,7 +639,7 @@
         <v>2</v>
       </c>
       <c r="I4" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -652,23 +652,23 @@
       <c r="C5" s="5">
         <v>0</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>3</v>
+      <c r="D5" s="6" t="s">
+        <v>4</v>
       </c>
       <c r="E5" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G5" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I5" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -681,11 +681,11 @@
       <c r="C6" s="5">
         <v>0</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>2</v>
+      <c r="D6" s="6" t="s">
+        <v>1</v>
       </c>
       <c r="E6" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" s="3">
         <v>0</v>
@@ -694,10 +694,10 @@
         <v>0</v>
       </c>
       <c r="H6" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I6" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -708,10 +708,10 @@
         <v>1</v>
       </c>
       <c r="C7" s="5">
-        <v>0</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>1</v>
       </c>
       <c r="E7" s="3">
         <v>0</v>
@@ -720,13 +720,13 @@
         <v>0</v>
       </c>
       <c r="G7" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H7" s="3">
         <v>0</v>
       </c>
       <c r="I7" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -740,22 +740,22 @@
         <v>0</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E8" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I8" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -769,22 +769,22 @@
         <v>0</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E9" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G9" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -798,22 +798,22 @@
         <v>0</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E10" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" s="3">
         <v>2</v>
       </c>
       <c r="G10" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H10" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -824,16 +824,16 @@
         <v>1</v>
       </c>
       <c r="C11" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E11" s="3">
         <v>0</v>
       </c>
       <c r="F11" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G11" s="3">
         <v>0</v>
@@ -859,7 +859,7 @@
         <v>3</v>
       </c>
       <c r="E12" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F12" s="3">
         <v>1</v>
@@ -868,108 +868,324 @@
         <v>0</v>
       </c>
       <c r="H12" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="8">
         <v>12</v>
       </c>
+      <c r="B13" s="4">
+        <v>1</v>
+      </c>
+      <c r="C13" s="5">
+        <v>0</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E13" s="3">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3">
+        <v>1</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0</v>
+      </c>
+      <c r="H13" s="3">
+        <v>2</v>
+      </c>
+      <c r="I13" s="3">
+        <v>2</v>
+      </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="8">
         <v>13</v>
       </c>
+      <c r="B14" s="4">
+        <v>1</v>
+      </c>
+      <c r="C14" s="5">
+        <v>0</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
+        <v>2</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
+        <v>2</v>
+      </c>
+      <c r="I14" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="8">
         <v>14</v>
       </c>
+      <c r="B15" s="4">
+        <v>1</v>
+      </c>
+      <c r="C15" s="5">
+        <v>0</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E15" s="3">
+        <v>1</v>
+      </c>
+      <c r="F15" s="3">
+        <v>0</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="3">
+        <v>0</v>
+      </c>
+      <c r="I15" s="3">
+        <v>2</v>
+      </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="8">
         <v>15</v>
       </c>
-    </row>
-    <row r="17" spans="1:1">
+      <c r="B16" s="4">
+        <v>1</v>
+      </c>
+      <c r="C16" s="5">
+        <v>0</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E16" s="3">
+        <v>0</v>
+      </c>
+      <c r="F16" s="3">
+        <v>0</v>
+      </c>
+      <c r="G16" s="3">
+        <v>0</v>
+      </c>
+      <c r="H16" s="3">
+        <v>0</v>
+      </c>
+      <c r="I16" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
       <c r="A17" s="8">
         <v>16</v>
       </c>
-    </row>
-    <row r="18" spans="1:1">
+      <c r="B17" s="4">
+        <v>1</v>
+      </c>
+      <c r="C17" s="5">
+        <v>0</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E17" s="3">
+        <v>1</v>
+      </c>
+      <c r="F17" s="3">
+        <v>1</v>
+      </c>
+      <c r="G17" s="3">
+        <v>0</v>
+      </c>
+      <c r="H17" s="3">
+        <v>1</v>
+      </c>
+      <c r="I17" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
       <c r="A18" s="8">
         <v>17</v>
       </c>
-    </row>
-    <row r="19" spans="1:1">
+      <c r="B18" s="4">
+        <v>1</v>
+      </c>
+      <c r="C18" s="5">
+        <v>0</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E18" s="3">
+        <v>0</v>
+      </c>
+      <c r="F18" s="3">
+        <v>2</v>
+      </c>
+      <c r="G18" s="3">
+        <v>0</v>
+      </c>
+      <c r="H18" s="3">
+        <v>0</v>
+      </c>
+      <c r="I18" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
       <c r="A19" s="8">
         <v>18</v>
       </c>
-    </row>
-    <row r="20" spans="1:1">
+      <c r="B19" s="4">
+        <v>1</v>
+      </c>
+      <c r="C19" s="5">
+        <v>0</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E19" s="3">
+        <v>0</v>
+      </c>
+      <c r="F19" s="3">
+        <v>2</v>
+      </c>
+      <c r="G19" s="3">
+        <v>2</v>
+      </c>
+      <c r="H19" s="3">
+        <v>0</v>
+      </c>
+      <c r="I19" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
       <c r="A20" s="8">
         <v>19</v>
       </c>
-    </row>
-    <row r="21" spans="1:1">
+      <c r="B20" s="4">
+        <v>1</v>
+      </c>
+      <c r="C20" s="5">
+        <v>0</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
+        <v>3</v>
+      </c>
+      <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
       <c r="A21" s="8">
         <v>20</v>
       </c>
-    </row>
-    <row r="22" spans="1:1">
+      <c r="B21" s="4">
+        <v>1</v>
+      </c>
+      <c r="C21" s="5">
+        <v>0</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E21" s="3">
+        <v>1</v>
+      </c>
+      <c r="F21" s="3">
+        <v>1</v>
+      </c>
+      <c r="G21" s="3">
+        <v>0</v>
+      </c>
+      <c r="H21" s="3">
+        <v>1</v>
+      </c>
+      <c r="I21" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
       <c r="A22" s="8">
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:1">
+    <row r="23" spans="1:9">
       <c r="A23" s="8">
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:1">
+    <row r="24" spans="1:9">
       <c r="A24" s="8">
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:1">
+    <row r="25" spans="1:9">
       <c r="A25" s="8">
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:1">
+    <row r="26" spans="1:9">
       <c r="A26" s="8">
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:1">
+    <row r="27" spans="1:9">
       <c r="A27" s="8">
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:1">
+    <row r="28" spans="1:9">
       <c r="A28" s="8">
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:1">
+    <row r="29" spans="1:9">
       <c r="A29" s="8">
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:1">
+    <row r="30" spans="1:9">
       <c r="A30" s="8">
         <v>29</v>
       </c>
     </row>
-    <row r="31" spans="1:1">
+    <row r="31" spans="1:9">
       <c r="A31" s="8">
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:1">
+    <row r="32" spans="1:9">
       <c r="A32" s="8">
         <v>31</v>
       </c>

--- a/data_of_card.xlsx
+++ b/data_of_card.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25831"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\GitHub\splendor-game\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\GitHub\splendor-game\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{457B7B8F-B9D5-480F-942D-1767F7F18A27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{815B5AFB-E993-4F44-B8AE-0A8910196276}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{9E734FED-030D-4E04-BF37-A3C9E4A43756}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9E734FED-030D-4E04-BF37-A3C9E4A43756}"/>
   </bookViews>
   <sheets>
     <sheet name="dev_card" sheetId="1" r:id="rId1"/>
@@ -89,11 +89,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <charset val="222"/>
       <scheme val="minor"/>
@@ -219,9 +219,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -259,7 +259,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -365,7 +365,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -507,7 +507,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -516,17 +516,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54A96224-6DA4-4492-BCD2-DBFE371CEB0B}">
   <dimension ref="A1:Q91"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" zeroHeight="1"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="13.8" zeroHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.77734375" style="8"/>
-    <col min="2" max="2" width="8.77734375" style="4"/>
-    <col min="3" max="3" width="8.77734375" style="5"/>
-    <col min="4" max="4" width="10.77734375" style="2" customWidth="1"/>
-    <col min="5" max="9" width="8.77734375" style="3"/>
-    <col min="18" max="16384" width="8.77734375" style="1"/>
+    <col min="1" max="1" width="8.796875" style="8"/>
+    <col min="2" max="2" width="8.796875" style="4"/>
+    <col min="3" max="3" width="8.796875" style="5"/>
+    <col min="4" max="4" width="10.796875" style="2" customWidth="1"/>
+    <col min="5" max="9" width="8.796875" style="3"/>
+    <col min="18" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
         <v>18</v>
       </c>
@@ -555,7 +555,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="8">
         <v>1</v>
       </c>
@@ -584,7 +584,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="8">
         <v>2</v>
       </c>
@@ -613,7 +613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="8">
         <v>3</v>
       </c>
@@ -642,7 +642,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="8">
         <v>4</v>
       </c>
@@ -671,7 +671,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="8">
         <v>5</v>
       </c>
@@ -700,7 +700,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="8">
         <v>6</v>
       </c>
@@ -729,7 +729,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="8">
         <v>7</v>
       </c>
@@ -758,7 +758,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="8">
         <v>8</v>
       </c>
@@ -787,7 +787,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="8">
         <v>9</v>
       </c>
@@ -816,7 +816,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="8">
         <v>10</v>
       </c>
@@ -845,7 +845,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="8">
         <v>11</v>
       </c>
@@ -874,302 +874,302 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="8">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:9">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="8">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="8">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:9">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="8">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:1">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="8">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:1">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="8">
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:1">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="8">
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:1">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="8">
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:1">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="8">
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:1">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="8">
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:1">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="8">
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:1">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="8">
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:1">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="8">
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:1">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="8">
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:1">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" s="8">
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:1">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="8">
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:1">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" s="8">
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:1">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" s="8">
         <v>29</v>
       </c>
     </row>
-    <row r="31" spans="1:1">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" s="8">
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:1">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" s="8">
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:1">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="8">
         <v>32</v>
       </c>
     </row>
-    <row r="34" spans="1:1">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" s="8">
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="1:1">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" s="8">
         <v>34</v>
       </c>
     </row>
-    <row r="36" spans="1:1">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" s="8">
         <v>35</v>
       </c>
     </row>
-    <row r="37" spans="1:1">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" s="8">
         <v>36</v>
       </c>
     </row>
-    <row r="38" spans="1:1">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" s="8">
         <v>37</v>
       </c>
     </row>
-    <row r="39" spans="1:1">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" s="8">
         <v>38</v>
       </c>
     </row>
-    <row r="40" spans="1:1">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" s="8">
         <v>39</v>
       </c>
     </row>
-    <row r="41" spans="1:1">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" s="8">
         <v>40</v>
       </c>
     </row>
-    <row r="42" spans="1:1">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" s="8">
         <v>41</v>
       </c>
     </row>
-    <row r="43" spans="1:1">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" s="8">
         <v>42</v>
       </c>
     </row>
-    <row r="44" spans="1:1">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" s="8">
         <v>43</v>
       </c>
     </row>
-    <row r="45" spans="1:1">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" s="8">
         <v>44</v>
       </c>
     </row>
-    <row r="46" spans="1:1">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" s="8">
         <v>45</v>
       </c>
     </row>
-    <row r="47" spans="1:1">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" s="8">
         <v>46</v>
       </c>
     </row>
-    <row r="48" spans="1:1">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" s="8">
         <v>47</v>
       </c>
     </row>
-    <row r="49" spans="1:1">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" s="8">
         <v>48</v>
       </c>
     </row>
-    <row r="50" spans="1:1">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" s="8">
         <v>49</v>
       </c>
     </row>
-    <row r="51" spans="1:1">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" s="8">
         <v>50</v>
       </c>
     </row>
-    <row r="52" spans="1:1">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" s="8">
         <v>51</v>
       </c>
     </row>
-    <row r="53" spans="1:1">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" s="8">
         <v>52</v>
       </c>
     </row>
-    <row r="54" spans="1:1">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" s="8">
         <v>53</v>
       </c>
     </row>
-    <row r="55" spans="1:1">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" s="8">
         <v>54</v>
       </c>
     </row>
-    <row r="56" spans="1:1">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" s="8">
         <v>55</v>
       </c>
     </row>
-    <row r="57" spans="1:1">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" s="8">
         <v>56</v>
       </c>
     </row>
-    <row r="58" spans="1:1">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" s="8">
         <v>57</v>
       </c>
     </row>
-    <row r="59" spans="1:1">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59" s="8">
         <v>58</v>
       </c>
     </row>
-    <row r="60" spans="1:1">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" s="8">
         <v>59</v>
       </c>
     </row>
-    <row r="61" spans="1:1">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61" s="8">
         <v>60</v>
       </c>
     </row>
-    <row r="62" spans="1:1">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62" s="8">
         <v>61</v>
       </c>
     </row>
-    <row r="63" spans="1:1">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A63" s="8">
         <v>62</v>
       </c>
     </row>
-    <row r="64" spans="1:1">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64" s="8">
         <v>63</v>
       </c>
     </row>
-    <row r="65" spans="1:11">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" s="8">
         <v>64</v>
       </c>
     </row>
-    <row r="66" spans="1:11">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="8">
         <v>65</v>
       </c>
     </row>
-    <row r="67" spans="1:11">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" s="8">
         <v>66</v>
       </c>
     </row>
-    <row r="68" spans="1:11">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" s="8">
         <v>67</v>
       </c>
     </row>
-    <row r="69" spans="1:11">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" s="8">
         <v>68</v>
       </c>
     </row>
-    <row r="70" spans="1:11">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" s="8">
         <v>69</v>
       </c>
     </row>
-    <row r="71" spans="1:11">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" s="8">
         <v>70</v>
       </c>
     </row>
-    <row r="72" spans="1:11">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" s="8">
         <v>71</v>
       </c>
@@ -1198,7 +1198,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="73" spans="1:11">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" s="8">
         <v>72</v>
       </c>
@@ -1227,7 +1227,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="74" spans="1:11">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" s="8">
         <v>73</v>
       </c>
@@ -1256,7 +1256,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:11">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" s="8">
         <v>74</v>
       </c>
@@ -1285,7 +1285,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:11">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" s="8">
         <v>75</v>
       </c>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="K76" s="1"/>
     </row>
-    <row r="77" spans="1:11">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" s="8">
         <v>76</v>
       </c>
@@ -1345,7 +1345,7 @@
       </c>
       <c r="K77" s="1"/>
     </row>
-    <row r="78" spans="1:11">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" s="8">
         <v>77</v>
       </c>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="K78" s="1"/>
     </row>
-    <row r="79" spans="1:11">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" s="8">
         <v>78</v>
       </c>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="K79" s="1"/>
     </row>
-    <row r="80" spans="1:11">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" s="8">
         <v>79</v>
       </c>
@@ -1435,7 +1435,7 @@
       </c>
       <c r="K80" s="1"/>
     </row>
-    <row r="81" spans="1:9">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" s="8">
         <v>80</v>
       </c>
@@ -1464,7 +1464,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:9">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" s="8">
         <v>81</v>
       </c>
@@ -1493,7 +1493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:9">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" s="8">
         <v>82</v>
       </c>
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:9">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" s="8">
         <v>83</v>
       </c>
@@ -1551,7 +1551,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="85" spans="1:9">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" s="8">
         <v>84</v>
       </c>
@@ -1580,7 +1580,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="86" spans="1:9">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" s="8">
         <v>85</v>
       </c>
@@ -1609,7 +1609,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="87" spans="1:9">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" s="8">
         <v>86</v>
       </c>
@@ -1638,7 +1638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:9">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" s="8">
         <v>87</v>
       </c>
@@ -1667,7 +1667,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="89" spans="1:9">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" s="8">
         <v>88</v>
       </c>
@@ -1696,7 +1696,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="90" spans="1:9">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" s="8">
         <v>89</v>
       </c>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:9">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" s="8">
         <v>90</v>
       </c>
@@ -1762,15 +1762,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E647C6B-A2D8-48B7-8561-74D848E3342C}">
   <dimension ref="A1:G11"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" zeroHeight="1"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="13.8" zeroHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.77734375" style="8"/>
-    <col min="2" max="2" width="8.77734375" style="5"/>
-    <col min="3" max="7" width="8.77734375" style="3"/>
-    <col min="8" max="16384" width="8.77734375" style="1"/>
+    <col min="1" max="1" width="8.796875" style="8"/>
+    <col min="2" max="2" width="8.796875" style="5"/>
+    <col min="3" max="7" width="8.796875" style="3"/>
+    <col min="8" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
         <v>18</v>
       </c>
@@ -1793,7 +1793,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="8">
         <v>91</v>
       </c>
@@ -1816,7 +1816,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="8">
         <v>92</v>
       </c>
@@ -1839,7 +1839,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="8">
         <v>93</v>
       </c>
@@ -1862,7 +1862,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="8">
         <v>94</v>
       </c>
@@ -1885,7 +1885,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="8">
         <v>95</v>
       </c>
@@ -1908,27 +1908,27 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="8">
         <v>96</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="8">
         <v>97</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="8">
         <v>98</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="8">
         <v>99</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="8">
         <v>100</v>
       </c>

--- a/data_of_card.xlsx
+++ b/data_of_card.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\GitHub\splendor-game\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Documents\GitHub\splendor-game\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB385A1A-A7C2-404E-9A61-307FE578BAD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8491470-B5E8-464A-B33F-5B4B837C320F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{9E734FED-030D-4E04-BF37-A3C9E4A43756}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{9E734FED-030D-4E04-BF37-A3C9E4A43756}"/>
   </bookViews>
   <sheets>
     <sheet name="dev_card" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="19">
   <si>
     <t>score</t>
   </si>
@@ -219,9 +219,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -259,7 +259,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -365,7 +365,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -507,7 +507,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1139,133 +1139,613 @@
       <c r="A22" s="8">
         <v>21</v>
       </c>
+      <c r="B22" s="4">
+        <v>1</v>
+      </c>
+      <c r="C22" s="5">
+        <v>0</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E22" s="3">
+        <v>2</v>
+      </c>
+      <c r="F22" s="3">
+        <v>1</v>
+      </c>
+      <c r="G22" s="3">
+        <v>1</v>
+      </c>
+      <c r="H22" s="3">
+        <v>0</v>
+      </c>
+      <c r="I22" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="8">
         <v>22</v>
       </c>
+      <c r="B23" s="4">
+        <v>1</v>
+      </c>
+      <c r="C23" s="5">
+        <v>0</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E23" s="3">
+        <v>0</v>
+      </c>
+      <c r="F23" s="3">
+        <v>1</v>
+      </c>
+      <c r="G23" s="3">
+        <v>2</v>
+      </c>
+      <c r="H23" s="3">
+        <v>1</v>
+      </c>
+      <c r="I23" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" s="8">
         <v>23</v>
       </c>
+      <c r="B24" s="4">
+        <v>1</v>
+      </c>
+      <c r="C24" s="5">
+        <v>0</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3">
+        <v>2</v>
+      </c>
+      <c r="H24" s="3">
+        <v>1</v>
+      </c>
+      <c r="I24" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="8">
         <v>24</v>
       </c>
+      <c r="B25" s="4">
+        <v>1</v>
+      </c>
+      <c r="C25" s="5">
+        <v>0</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E25" s="3">
+        <v>2</v>
+      </c>
+      <c r="F25" s="3">
+        <v>2</v>
+      </c>
+      <c r="G25" s="3">
+        <v>0</v>
+      </c>
+      <c r="H25" s="3">
+        <v>1</v>
+      </c>
+      <c r="I25" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="8">
         <v>25</v>
       </c>
+      <c r="B26" s="4">
+        <v>1</v>
+      </c>
+      <c r="C26" s="5">
+        <v>0</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E26" s="3">
+        <v>2</v>
+      </c>
+      <c r="F26" s="3">
+        <v>0</v>
+      </c>
+      <c r="G26" s="3">
+        <v>2</v>
+      </c>
+      <c r="H26" s="3">
+        <v>0</v>
+      </c>
+      <c r="I26" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="8">
         <v>26</v>
       </c>
+      <c r="B27" s="4">
+        <v>1</v>
+      </c>
+      <c r="C27" s="5">
+        <v>0</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E27" s="3">
+        <v>3</v>
+      </c>
+      <c r="F27" s="3">
+        <v>1</v>
+      </c>
+      <c r="G27" s="3">
+        <v>0</v>
+      </c>
+      <c r="H27" s="3">
+        <v>0</v>
+      </c>
+      <c r="I27" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="28" spans="1:9">
       <c r="A28" s="8">
         <v>27</v>
       </c>
+      <c r="B28" s="4">
+        <v>1</v>
+      </c>
+      <c r="C28" s="5">
+        <v>0</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E28" s="3">
+        <v>2</v>
+      </c>
+      <c r="F28" s="3">
+        <v>0</v>
+      </c>
+      <c r="G28" s="3">
+        <v>1</v>
+      </c>
+      <c r="H28" s="3">
+        <v>0</v>
+      </c>
+      <c r="I28" s="3">
+        <v>2</v>
+      </c>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" s="8">
         <v>28</v>
       </c>
+      <c r="B29" s="4">
+        <v>1</v>
+      </c>
+      <c r="C29" s="5">
+        <v>0</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E29" s="3">
+        <v>3</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" s="8">
         <v>29</v>
       </c>
+      <c r="B30" s="4">
+        <v>1</v>
+      </c>
+      <c r="C30" s="5">
+        <v>0</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E30" s="3">
+        <v>0</v>
+      </c>
+      <c r="F30" s="3">
+        <v>2</v>
+      </c>
+      <c r="G30" s="3">
+        <v>1</v>
+      </c>
+      <c r="H30" s="3">
+        <v>0</v>
+      </c>
+      <c r="I30" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" s="8">
         <v>30</v>
       </c>
+      <c r="B31" s="4">
+        <v>1</v>
+      </c>
+      <c r="C31" s="5">
+        <v>0</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E31" s="3">
+        <v>1</v>
+      </c>
+      <c r="F31" s="3">
+        <v>0</v>
+      </c>
+      <c r="G31" s="3">
+        <v>0</v>
+      </c>
+      <c r="H31" s="3">
+        <v>1</v>
+      </c>
+      <c r="I31" s="3">
+        <v>3</v>
+      </c>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" s="8">
         <v>31</v>
       </c>
-    </row>
-    <row r="33" spans="1:1">
+      <c r="B32" s="4">
+        <v>1</v>
+      </c>
+      <c r="C32" s="5">
+        <v>0</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E32" s="3">
+        <v>1</v>
+      </c>
+      <c r="F32" s="3">
+        <v>3</v>
+      </c>
+      <c r="G32" s="3">
+        <v>1</v>
+      </c>
+      <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
       <c r="A33" s="8">
         <v>32</v>
       </c>
-    </row>
-    <row r="34" spans="1:1">
+      <c r="B33" s="4">
+        <v>1</v>
+      </c>
+      <c r="C33" s="5">
+        <v>0</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E33" s="3">
+        <v>1</v>
+      </c>
+      <c r="F33" s="3">
+        <v>0</v>
+      </c>
+      <c r="G33" s="3">
+        <v>1</v>
+      </c>
+      <c r="H33" s="3">
+        <v>1</v>
+      </c>
+      <c r="I33" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
       <c r="A34" s="8">
         <v>33</v>
       </c>
-    </row>
-    <row r="35" spans="1:1">
+      <c r="B34" s="4">
+        <v>1</v>
+      </c>
+      <c r="C34" s="5">
+        <v>0</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E34" s="3">
+        <v>0</v>
+      </c>
+      <c r="F34" s="3">
+        <v>1</v>
+      </c>
+      <c r="G34" s="3">
+        <v>1</v>
+      </c>
+      <c r="H34" s="3">
+        <v>1</v>
+      </c>
+      <c r="I34" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
       <c r="A35" s="8">
         <v>34</v>
       </c>
-    </row>
-    <row r="36" spans="1:1">
+      <c r="B35" s="4">
+        <v>1</v>
+      </c>
+      <c r="C35" s="5">
+        <v>0</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E35" s="3">
+        <v>0</v>
+      </c>
+      <c r="F35" s="3">
+        <v>0</v>
+      </c>
+      <c r="G35" s="3">
+        <v>3</v>
+      </c>
+      <c r="H35" s="3">
+        <v>0</v>
+      </c>
+      <c r="I35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
       <c r="A36" s="8">
         <v>35</v>
       </c>
-    </row>
-    <row r="37" spans="1:1">
+      <c r="B36" s="4">
+        <v>1</v>
+      </c>
+      <c r="C36" s="5">
+        <v>0</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E36" s="3">
+        <v>0</v>
+      </c>
+      <c r="F36" s="3">
+        <v>1</v>
+      </c>
+      <c r="G36" s="3">
+        <v>3</v>
+      </c>
+      <c r="H36" s="3">
+        <v>1</v>
+      </c>
+      <c r="I36" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
       <c r="A37" s="8">
         <v>36</v>
       </c>
-    </row>
-    <row r="38" spans="1:1">
+      <c r="B37" s="4">
+        <v>1</v>
+      </c>
+      <c r="C37" s="5">
+        <v>0</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E37" s="3">
+        <v>0</v>
+      </c>
+      <c r="F37" s="3">
+        <v>0</v>
+      </c>
+      <c r="G37" s="3">
+        <v>0</v>
+      </c>
+      <c r="H37" s="3">
+        <v>3</v>
+      </c>
+      <c r="I37" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9">
       <c r="A38" s="8">
         <v>37</v>
       </c>
-    </row>
-    <row r="39" spans="1:1">
+      <c r="B38" s="4">
+        <v>1</v>
+      </c>
+      <c r="C38" s="5">
+        <v>0</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E38" s="3">
+        <v>0</v>
+      </c>
+      <c r="F38" s="3">
+        <v>0</v>
+      </c>
+      <c r="G38" s="3">
+        <v>2</v>
+      </c>
+      <c r="H38" s="3">
+        <v>0</v>
+      </c>
+      <c r="I38" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9">
       <c r="A39" s="8">
         <v>38</v>
       </c>
-    </row>
-    <row r="40" spans="1:1">
+      <c r="B39" s="4">
+        <v>1</v>
+      </c>
+      <c r="C39" s="5">
+        <v>1</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E39" s="3">
+        <v>0</v>
+      </c>
+      <c r="F39" s="3">
+        <v>0</v>
+      </c>
+      <c r="G39" s="3">
+        <v>0</v>
+      </c>
+      <c r="H39" s="3">
+        <v>4</v>
+      </c>
+      <c r="I39" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9">
       <c r="A40" s="8">
         <v>39</v>
       </c>
-    </row>
-    <row r="41" spans="1:1">
+      <c r="B40" s="4">
+        <v>1</v>
+      </c>
+      <c r="C40" s="5">
+        <v>1</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E40" s="3">
+        <v>0</v>
+      </c>
+      <c r="F40" s="3">
+        <v>0</v>
+      </c>
+      <c r="G40" s="3">
+        <v>0</v>
+      </c>
+      <c r="H40" s="3">
+        <v>0</v>
+      </c>
+      <c r="I40" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9">
       <c r="A41" s="8">
         <v>40</v>
       </c>
-    </row>
-    <row r="42" spans="1:1">
+      <c r="B41" s="4">
+        <v>1</v>
+      </c>
+      <c r="C41" s="5">
+        <v>1</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E41" s="3">
+        <v>4</v>
+      </c>
+      <c r="F41" s="3">
+        <v>0</v>
+      </c>
+      <c r="G41" s="3">
+        <v>0</v>
+      </c>
+      <c r="H41" s="3">
+        <v>0</v>
+      </c>
+      <c r="I41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9">
       <c r="A42" s="8">
         <v>41</v>
       </c>
     </row>
-    <row r="43" spans="1:1">
+    <row r="43" spans="1:9">
       <c r="A43" s="8">
         <v>42</v>
       </c>
     </row>
-    <row r="44" spans="1:1">
+    <row r="44" spans="1:9">
       <c r="A44" s="8">
         <v>43</v>
       </c>
     </row>
-    <row r="45" spans="1:1">
+    <row r="45" spans="1:9">
       <c r="A45" s="8">
         <v>44</v>
       </c>
     </row>
-    <row r="46" spans="1:1">
+    <row r="46" spans="1:9">
       <c r="A46" s="8">
         <v>45</v>
       </c>
     </row>
-    <row r="47" spans="1:1">
+    <row r="47" spans="1:9">
       <c r="A47" s="8">
         <v>46</v>
       </c>
     </row>
-    <row r="48" spans="1:1">
+    <row r="48" spans="1:9">
       <c r="A48" s="8">
         <v>47</v>
       </c>
@@ -2014,22 +2494,22 @@
         <v>91</v>
       </c>
       <c r="B2" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C2" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D2" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E2" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2" s="3">
         <v>3</v>
       </c>
       <c r="G2" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -2040,19 +2520,19 @@
         <v>3</v>
       </c>
       <c r="C3" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D3" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E3" s="3">
         <v>4</v>
       </c>
       <c r="F3" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G3" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -2063,19 +2543,19 @@
         <v>3</v>
       </c>
       <c r="C4" s="3">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D4" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E4" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F4" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G4" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -2086,19 +2566,19 @@
         <v>3</v>
       </c>
       <c r="C5" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D5" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E5" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F5" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G5" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -2109,44 +2589,134 @@
         <v>3</v>
       </c>
       <c r="C6" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D6" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E6" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F6" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G6" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="8">
         <v>96</v>
       </c>
+      <c r="B7" s="5">
+        <v>3</v>
+      </c>
+      <c r="C7" s="3">
+        <v>4</v>
+      </c>
+      <c r="D7" s="3">
+        <v>4</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3">
+        <v>0</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="8">
         <v>97</v>
       </c>
+      <c r="B8" s="5">
+        <v>3</v>
+      </c>
+      <c r="C8" s="3">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
+        <v>4</v>
+      </c>
+      <c r="G8" s="3">
+        <v>4</v>
+      </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="8">
         <v>98</v>
       </c>
+      <c r="B9" s="5">
+        <v>3</v>
+      </c>
+      <c r="C9" s="3">
+        <v>3</v>
+      </c>
+      <c r="D9" s="3">
+        <v>3</v>
+      </c>
+      <c r="E9" s="3">
+        <v>3</v>
+      </c>
+      <c r="F9" s="3">
+        <v>0</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="8">
         <v>99</v>
       </c>
+      <c r="B10" s="5">
+        <v>3</v>
+      </c>
+      <c r="C10" s="3">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3">
+        <v>3</v>
+      </c>
+      <c r="E10" s="3">
+        <v>3</v>
+      </c>
+      <c r="F10" s="3">
+        <v>3</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="8">
         <v>100</v>
+      </c>
+      <c r="B11" s="5">
+        <v>3</v>
+      </c>
+      <c r="C11" s="3">
+        <v>3</v>
+      </c>
+      <c r="D11" s="3">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3">
+        <v>3</v>
+      </c>
+      <c r="G11" s="3">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/data_of_card.xlsx
+++ b/data_of_card.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25831"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Documents\GitHub\splendor-game\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\GitHub\splendor-game\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8491470-B5E8-464A-B33F-5B4B837C320F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D35AB8A-5337-4DFA-9233-78459B10E5C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{9E734FED-030D-4E04-BF37-A3C9E4A43756}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9E734FED-030D-4E04-BF37-A3C9E4A43756}"/>
   </bookViews>
   <sheets>
     <sheet name="dev_card" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="19">
   <si>
     <t>score</t>
   </si>
@@ -89,11 +89,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <charset val="222"/>
       <scheme val="minor"/>
@@ -516,17 +516,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54A96224-6DA4-4492-BCD2-DBFE371CEB0B}">
   <dimension ref="A1:Q91"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" zeroHeight="1"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="13.8" zeroHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.77734375" style="8"/>
-    <col min="2" max="2" width="8.77734375" style="4"/>
-    <col min="3" max="3" width="8.77734375" style="5"/>
-    <col min="4" max="4" width="10.77734375" style="2" customWidth="1"/>
-    <col min="5" max="9" width="8.77734375" style="3"/>
-    <col min="18" max="16384" width="8.77734375" style="1"/>
+    <col min="1" max="1" width="8.796875" style="8"/>
+    <col min="2" max="2" width="8.796875" style="4"/>
+    <col min="3" max="3" width="8.796875" style="5"/>
+    <col min="4" max="4" width="10.796875" style="2" customWidth="1"/>
+    <col min="5" max="9" width="8.796875" style="3"/>
+    <col min="18" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
         <v>18</v>
       </c>
@@ -555,7 +555,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="8">
         <v>1</v>
       </c>
@@ -584,7 +584,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="8">
         <v>2</v>
       </c>
@@ -613,7 +613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="8">
         <v>3</v>
       </c>
@@ -642,7 +642,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="8">
         <v>4</v>
       </c>
@@ -671,7 +671,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="8">
         <v>5</v>
       </c>
@@ -700,7 +700,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="8">
         <v>6</v>
       </c>
@@ -729,7 +729,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="8">
         <v>7</v>
       </c>
@@ -758,7 +758,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="8">
         <v>8</v>
       </c>
@@ -787,7 +787,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="8">
         <v>9</v>
       </c>
@@ -816,7 +816,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="8">
         <v>10</v>
       </c>
@@ -845,7 +845,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="8">
         <v>11</v>
       </c>
@@ -874,7 +874,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="8">
         <v>12</v>
       </c>
@@ -903,7 +903,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:9">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="8">
         <v>13</v>
       </c>
@@ -932,7 +932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="8">
         <v>14</v>
       </c>
@@ -961,7 +961,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:9">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="8">
         <v>15</v>
       </c>
@@ -990,7 +990,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:9">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="8">
         <v>16</v>
       </c>
@@ -1019,7 +1019,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:9">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="8">
         <v>17</v>
       </c>
@@ -1048,7 +1048,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:9">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="8">
         <v>18</v>
       </c>
@@ -1077,7 +1077,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:9">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="8">
         <v>19</v>
       </c>
@@ -1106,7 +1106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:9">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="8">
         <v>20</v>
       </c>
@@ -1135,7 +1135,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:9">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="8">
         <v>21</v>
       </c>
@@ -1164,7 +1164,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:9">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="8">
         <v>22</v>
       </c>
@@ -1193,7 +1193,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:9">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="8">
         <v>23</v>
       </c>
@@ -1222,7 +1222,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:9">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="8">
         <v>24</v>
       </c>
@@ -1251,7 +1251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:9">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="8">
         <v>25</v>
       </c>
@@ -1280,7 +1280,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:9">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="8">
         <v>26</v>
       </c>
@@ -1309,7 +1309,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:9">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="8">
         <v>27</v>
       </c>
@@ -1338,7 +1338,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:9">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="8">
         <v>28</v>
       </c>
@@ -1367,7 +1367,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:9">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="8">
         <v>29</v>
       </c>
@@ -1396,7 +1396,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:9">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="8">
         <v>30</v>
       </c>
@@ -1425,7 +1425,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="1:9">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="8">
         <v>31</v>
       </c>
@@ -1454,7 +1454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:9">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="8">
         <v>32</v>
       </c>
@@ -1483,7 +1483,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:9">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="8">
         <v>33</v>
       </c>
@@ -1512,7 +1512,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:9">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="8">
         <v>34</v>
       </c>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:9">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="8">
         <v>35</v>
       </c>
@@ -1570,7 +1570,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:9">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="8">
         <v>36</v>
       </c>
@@ -1599,7 +1599,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:9">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="8">
         <v>37</v>
       </c>
@@ -1628,7 +1628,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="1:9">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="8">
         <v>38</v>
       </c>
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:9">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="8">
         <v>39</v>
       </c>
@@ -1686,7 +1686,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="41" spans="1:9">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="8">
         <v>40</v>
       </c>
@@ -1715,157 +1715,877 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:9">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" s="8">
         <v>41</v>
       </c>
-    </row>
-    <row r="43" spans="1:9">
+      <c r="B42" s="4">
+        <v>2</v>
+      </c>
+      <c r="C42" s="5">
+        <v>1</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
+        <v>2</v>
+      </c>
+      <c r="G42" s="3">
+        <v>3</v>
+      </c>
+      <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="8">
         <v>42</v>
       </c>
-    </row>
-    <row r="44" spans="1:9">
+      <c r="B43" s="4">
+        <v>2</v>
+      </c>
+      <c r="C43" s="5">
+        <v>2</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E43" s="3">
+        <v>0</v>
+      </c>
+      <c r="F43" s="3">
+        <v>5</v>
+      </c>
+      <c r="G43" s="3">
+        <v>3</v>
+      </c>
+      <c r="H43" s="3">
+        <v>0</v>
+      </c>
+      <c r="I43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="8">
         <v>43</v>
       </c>
-    </row>
-    <row r="45" spans="1:9">
+      <c r="B44" s="4">
+        <v>2</v>
+      </c>
+      <c r="C44" s="5">
+        <v>1</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3">
+        <v>2</v>
+      </c>
+      <c r="F44" s="3">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3">
+        <v>0</v>
+      </c>
+      <c r="H44" s="3">
+        <v>0</v>
+      </c>
+      <c r="I44" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="8">
         <v>44</v>
       </c>
-    </row>
-    <row r="46" spans="1:9">
+      <c r="B45" s="4">
+        <v>2</v>
+      </c>
+      <c r="C45" s="5">
+        <v>1</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E45" s="3">
+        <v>3</v>
+      </c>
+      <c r="F45" s="3">
+        <v>2</v>
+      </c>
+      <c r="G45" s="3">
+        <v>2</v>
+      </c>
+      <c r="H45" s="3">
+        <v>0</v>
+      </c>
+      <c r="I45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="8">
         <v>45</v>
       </c>
-    </row>
-    <row r="47" spans="1:9">
+      <c r="B46" s="4">
+        <v>2</v>
+      </c>
+      <c r="C46" s="5">
+        <v>1</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E46" s="3">
+        <v>2</v>
+      </c>
+      <c r="F46" s="3">
+        <v>3</v>
+      </c>
+      <c r="G46" s="3">
+        <v>0</v>
+      </c>
+      <c r="H46" s="3">
+        <v>3</v>
+      </c>
+      <c r="I46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" s="8">
         <v>46</v>
       </c>
-    </row>
-    <row r="48" spans="1:9">
+      <c r="B47" s="4">
+        <v>2</v>
+      </c>
+      <c r="C47" s="5">
+        <v>2</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E47" s="3">
+        <v>0</v>
+      </c>
+      <c r="F47" s="3">
+        <v>0</v>
+      </c>
+      <c r="G47" s="3">
+        <v>1</v>
+      </c>
+      <c r="H47" s="3">
+        <v>4</v>
+      </c>
+      <c r="I47" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" s="8">
         <v>47</v>
       </c>
-    </row>
-    <row r="49" spans="1:1">
+      <c r="B48" s="4">
+        <v>2</v>
+      </c>
+      <c r="C48" s="5">
+        <v>2</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E48" s="3">
+        <v>2</v>
+      </c>
+      <c r="F48" s="3">
+        <v>0</v>
+      </c>
+      <c r="G48" s="3">
+        <v>0</v>
+      </c>
+      <c r="H48" s="3">
+        <v>1</v>
+      </c>
+      <c r="I48" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="8">
         <v>48</v>
       </c>
-    </row>
-    <row r="50" spans="1:1">
+      <c r="B49" s="4">
+        <v>2</v>
+      </c>
+      <c r="C49" s="5">
+        <v>2</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E49" s="3">
+        <v>0</v>
+      </c>
+      <c r="F49" s="3">
+        <v>1</v>
+      </c>
+      <c r="G49" s="3">
+        <v>4</v>
+      </c>
+      <c r="H49" s="3">
+        <v>2</v>
+      </c>
+      <c r="I49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="8">
         <v>49</v>
       </c>
-    </row>
-    <row r="51" spans="1:1">
+      <c r="B50" s="4">
+        <v>2</v>
+      </c>
+      <c r="C50" s="5">
+        <v>2</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E50" s="3">
+        <v>0</v>
+      </c>
+      <c r="F50" s="3">
+        <v>0</v>
+      </c>
+      <c r="G50" s="3">
+        <v>5</v>
+      </c>
+      <c r="H50" s="3">
+        <v>0</v>
+      </c>
+      <c r="I50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" s="8">
         <v>50</v>
       </c>
-    </row>
-    <row r="52" spans="1:1">
+      <c r="B51" s="4">
+        <v>2</v>
+      </c>
+      <c r="C51" s="5">
+        <v>2</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E51" s="3">
+        <v>0</v>
+      </c>
+      <c r="F51" s="3">
+        <v>0</v>
+      </c>
+      <c r="G51" s="3">
+        <v>0</v>
+      </c>
+      <c r="H51" s="3">
+        <v>5</v>
+      </c>
+      <c r="I51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" s="8">
         <v>51</v>
       </c>
-    </row>
-    <row r="53" spans="1:1">
+      <c r="B52" s="4">
+        <v>2</v>
+      </c>
+      <c r="C52" s="5">
+        <v>1</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E52" s="3">
+        <v>2</v>
+      </c>
+      <c r="F52" s="3">
+        <v>0</v>
+      </c>
+      <c r="G52" s="3">
+        <v>0</v>
+      </c>
+      <c r="H52" s="3">
+        <v>2</v>
+      </c>
+      <c r="I52" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" s="8">
         <v>52</v>
       </c>
-    </row>
-    <row r="54" spans="1:1">
+      <c r="B53" s="4">
+        <v>2</v>
+      </c>
+      <c r="C53" s="5">
+        <v>2</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E53" s="3">
+        <v>3</v>
+      </c>
+      <c r="F53" s="3">
+        <v>0</v>
+      </c>
+      <c r="G53" s="3">
+        <v>0</v>
+      </c>
+      <c r="H53" s="3">
+        <v>0</v>
+      </c>
+      <c r="I53" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="8">
         <v>53</v>
       </c>
-    </row>
-    <row r="55" spans="1:1">
+      <c r="B54" s="4">
+        <v>2</v>
+      </c>
+      <c r="C54" s="5">
+        <v>3</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E54" s="3">
+        <v>0</v>
+      </c>
+      <c r="F54" s="3">
+        <v>0</v>
+      </c>
+      <c r="G54" s="3">
+        <v>6</v>
+      </c>
+      <c r="H54" s="3">
+        <v>0</v>
+      </c>
+      <c r="I54" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="8">
         <v>54</v>
       </c>
-    </row>
-    <row r="56" spans="1:1">
+      <c r="B55" s="4">
+        <v>2</v>
+      </c>
+      <c r="C55" s="5">
+        <v>1</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E55" s="3">
+        <v>0</v>
+      </c>
+      <c r="F55" s="3">
+        <v>2</v>
+      </c>
+      <c r="G55" s="3">
+        <v>2</v>
+      </c>
+      <c r="H55" s="3">
+        <v>3</v>
+      </c>
+      <c r="I55" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" s="8">
         <v>55</v>
       </c>
-    </row>
-    <row r="57" spans="1:1">
+      <c r="B56" s="4">
+        <v>2</v>
+      </c>
+      <c r="C56" s="5">
+        <v>3</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E56" s="3">
+        <v>0</v>
+      </c>
+      <c r="F56" s="3">
+        <v>0</v>
+      </c>
+      <c r="G56" s="3">
+        <v>0</v>
+      </c>
+      <c r="H56" s="3">
+        <v>0</v>
+      </c>
+      <c r="I56" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" s="8">
         <v>56</v>
       </c>
-    </row>
-    <row r="58" spans="1:1">
+      <c r="B57" s="4">
+        <v>2</v>
+      </c>
+      <c r="C57" s="5">
+        <v>3</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E57" s="3">
+        <v>0</v>
+      </c>
+      <c r="F57" s="3">
+        <v>0</v>
+      </c>
+      <c r="G57" s="3">
+        <v>0</v>
+      </c>
+      <c r="H57" s="3">
+        <v>6</v>
+      </c>
+      <c r="I57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="8">
         <v>57</v>
       </c>
-    </row>
-    <row r="59" spans="1:1">
+      <c r="B58" s="4">
+        <v>2</v>
+      </c>
+      <c r="C58" s="5">
+        <v>1</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E58" s="3">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3">
+        <v>3</v>
+      </c>
+      <c r="G58" s="3">
+        <v>0</v>
+      </c>
+      <c r="H58" s="3">
+        <v>2</v>
+      </c>
+      <c r="I58" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" s="8">
         <v>58</v>
       </c>
-    </row>
-    <row r="60" spans="1:1">
+      <c r="B59" s="4">
+        <v>2</v>
+      </c>
+      <c r="C59" s="5">
+        <v>3</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E59" s="3">
+        <v>0</v>
+      </c>
+      <c r="F59" s="3">
+        <v>6</v>
+      </c>
+      <c r="G59" s="3">
+        <v>0</v>
+      </c>
+      <c r="H59" s="3">
+        <v>0</v>
+      </c>
+      <c r="I59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="8">
         <v>59</v>
       </c>
-    </row>
-    <row r="61" spans="1:1">
+      <c r="B60" s="4">
+        <v>2</v>
+      </c>
+      <c r="C60" s="5">
+        <v>2</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E60" s="3">
+        <v>0</v>
+      </c>
+      <c r="F60" s="3">
+        <v>5</v>
+      </c>
+      <c r="G60" s="3">
+        <v>0</v>
+      </c>
+      <c r="H60" s="3">
+        <v>0</v>
+      </c>
+      <c r="I60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="8">
         <v>60</v>
       </c>
-    </row>
-    <row r="62" spans="1:1">
+      <c r="B61" s="4">
+        <v>2</v>
+      </c>
+      <c r="C61" s="5">
+        <v>2</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E61" s="3">
+        <v>0</v>
+      </c>
+      <c r="F61" s="3">
+        <v>0</v>
+      </c>
+      <c r="G61" s="3">
+        <v>0</v>
+      </c>
+      <c r="H61" s="3">
+        <v>5</v>
+      </c>
+      <c r="I61" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="8">
         <v>61</v>
       </c>
-    </row>
-    <row r="63" spans="1:1">
+      <c r="B62" s="4">
+        <v>2</v>
+      </c>
+      <c r="C62" s="5">
+        <v>2</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E62" s="3">
+        <v>5</v>
+      </c>
+      <c r="F62" s="3">
+        <v>5</v>
+      </c>
+      <c r="G62" s="3">
+        <v>0</v>
+      </c>
+      <c r="H62" s="3">
+        <v>0</v>
+      </c>
+      <c r="I62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="8">
         <v>62</v>
       </c>
-    </row>
-    <row r="64" spans="1:1">
+      <c r="B63" s="4">
+        <v>2</v>
+      </c>
+      <c r="C63" s="5">
+        <v>1</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E63" s="3">
+        <v>3</v>
+      </c>
+      <c r="F63" s="3">
+        <v>0</v>
+      </c>
+      <c r="G63" s="3">
+        <v>3</v>
+      </c>
+      <c r="H63" s="3">
+        <v>0</v>
+      </c>
+      <c r="I63" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="8">
         <v>63</v>
       </c>
-    </row>
-    <row r="65" spans="1:11">
+      <c r="B64" s="4">
+        <v>2</v>
+      </c>
+      <c r="C64" s="5">
+        <v>2</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E64" s="3">
+        <v>1</v>
+      </c>
+      <c r="F64" s="3">
+        <v>4</v>
+      </c>
+      <c r="G64" s="3">
+        <v>2</v>
+      </c>
+      <c r="H64" s="3">
+        <v>0</v>
+      </c>
+      <c r="I64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" s="8">
         <v>64</v>
       </c>
-    </row>
-    <row r="66" spans="1:11">
+      <c r="B65" s="4">
+        <v>2</v>
+      </c>
+      <c r="C65" s="5">
+        <v>2</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E65" s="3">
+        <v>4</v>
+      </c>
+      <c r="F65" s="3">
+        <v>4</v>
+      </c>
+      <c r="G65" s="3">
+        <v>0</v>
+      </c>
+      <c r="H65" s="3">
+        <v>0</v>
+      </c>
+      <c r="I65" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="8">
         <v>65</v>
       </c>
-    </row>
-    <row r="67" spans="1:11">
+      <c r="B66" s="4">
+        <v>2</v>
+      </c>
+      <c r="C66" s="5">
+        <v>2</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E66" s="3">
+        <v>5</v>
+      </c>
+      <c r="F66" s="3">
+        <v>0</v>
+      </c>
+      <c r="G66" s="3">
+        <v>0</v>
+      </c>
+      <c r="H66" s="3">
+        <v>0</v>
+      </c>
+      <c r="I66" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" s="8">
         <v>66</v>
       </c>
-    </row>
-    <row r="68" spans="1:11">
+      <c r="B67" s="4">
+        <v>2</v>
+      </c>
+      <c r="C67" s="5">
+        <v>3</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E67" s="3">
+        <v>6</v>
+      </c>
+      <c r="F67" s="3">
+        <v>0</v>
+      </c>
+      <c r="G67" s="3">
+        <v>0</v>
+      </c>
+      <c r="H67" s="3">
+        <v>0</v>
+      </c>
+      <c r="I67" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" s="8">
         <v>67</v>
       </c>
-    </row>
-    <row r="69" spans="1:11">
+      <c r="B68" s="4">
+        <v>2</v>
+      </c>
+      <c r="C68" s="5">
+        <v>1</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E68" s="3">
+        <v>3</v>
+      </c>
+      <c r="F68" s="3">
+        <v>0</v>
+      </c>
+      <c r="G68" s="3">
+        <v>2</v>
+      </c>
+      <c r="H68" s="3">
+        <v>3</v>
+      </c>
+      <c r="I68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" s="8">
         <v>68</v>
       </c>
-    </row>
-    <row r="70" spans="1:11">
+      <c r="B69" s="4">
+        <v>2</v>
+      </c>
+      <c r="C69" s="5">
+        <v>1</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E69" s="3">
+        <v>0</v>
+      </c>
+      <c r="F69" s="3">
+        <v>0</v>
+      </c>
+      <c r="G69" s="3">
+        <v>3</v>
+      </c>
+      <c r="H69" s="3">
+        <v>2</v>
+      </c>
+      <c r="I69" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" s="8">
         <v>69</v>
       </c>
-    </row>
-    <row r="71" spans="1:11">
+      <c r="B70" s="4">
+        <v>2</v>
+      </c>
+      <c r="C70" s="5">
+        <v>2</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E70" s="3">
+        <v>0</v>
+      </c>
+      <c r="F70" s="3">
+        <v>0</v>
+      </c>
+      <c r="G70" s="3">
+        <v>0</v>
+      </c>
+      <c r="H70" s="3">
+        <v>0</v>
+      </c>
+      <c r="I70" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" s="8">
         <v>70</v>
       </c>
-    </row>
-    <row r="72" spans="1:11">
+      <c r="B71" s="4">
+        <v>2</v>
+      </c>
+      <c r="C71" s="5">
+        <v>2</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E71" s="3">
+        <v>0</v>
+      </c>
+      <c r="F71" s="3">
+        <v>0</v>
+      </c>
+      <c r="G71" s="3">
+        <v>5</v>
+      </c>
+      <c r="H71" s="3">
+        <v>3</v>
+      </c>
+      <c r="I71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" s="8">
         <v>71</v>
       </c>
@@ -1894,7 +2614,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="73" spans="1:11">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" s="8">
         <v>72</v>
       </c>
@@ -1923,7 +2643,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="74" spans="1:11">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" s="8">
         <v>73</v>
       </c>
@@ -1952,7 +2672,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:11">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" s="8">
         <v>74</v>
       </c>
@@ -1981,7 +2701,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:11">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" s="8">
         <v>75</v>
       </c>
@@ -2011,7 +2731,7 @@
       </c>
       <c r="K76" s="1"/>
     </row>
-    <row r="77" spans="1:11">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" s="8">
         <v>76</v>
       </c>
@@ -2041,7 +2761,7 @@
       </c>
       <c r="K77" s="1"/>
     </row>
-    <row r="78" spans="1:11">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" s="8">
         <v>77</v>
       </c>
@@ -2071,7 +2791,7 @@
       </c>
       <c r="K78" s="1"/>
     </row>
-    <row r="79" spans="1:11">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" s="8">
         <v>78</v>
       </c>
@@ -2101,7 +2821,7 @@
       </c>
       <c r="K79" s="1"/>
     </row>
-    <row r="80" spans="1:11">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" s="8">
         <v>79</v>
       </c>
@@ -2131,7 +2851,7 @@
       </c>
       <c r="K80" s="1"/>
     </row>
-    <row r="81" spans="1:9">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" s="8">
         <v>80</v>
       </c>
@@ -2160,7 +2880,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:9">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" s="8">
         <v>81</v>
       </c>
@@ -2189,7 +2909,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:9">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" s="8">
         <v>82</v>
       </c>
@@ -2218,7 +2938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:9">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" s="8">
         <v>83</v>
       </c>
@@ -2247,7 +2967,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="85" spans="1:9">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" s="8">
         <v>84</v>
       </c>
@@ -2276,7 +2996,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="86" spans="1:9">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" s="8">
         <v>85</v>
       </c>
@@ -2305,7 +3025,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="87" spans="1:9">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" s="8">
         <v>86</v>
       </c>
@@ -2334,7 +3054,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:9">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" s="8">
         <v>87</v>
       </c>
@@ -2363,7 +3083,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="89" spans="1:9">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" s="8">
         <v>88</v>
       </c>
@@ -2392,7 +3112,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="90" spans="1:9">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" s="8">
         <v>89</v>
       </c>
@@ -2421,7 +3141,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:9">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" s="8">
         <v>90</v>
       </c>
@@ -2458,15 +3178,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E647C6B-A2D8-48B7-8561-74D848E3342C}">
   <dimension ref="A1:G11"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" zeroHeight="1"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="13.8" zeroHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.77734375" style="8"/>
-    <col min="2" max="2" width="8.77734375" style="5"/>
-    <col min="3" max="7" width="8.77734375" style="3"/>
-    <col min="8" max="16384" width="8.77734375" style="1"/>
+    <col min="1" max="1" width="8.796875" style="8"/>
+    <col min="2" max="2" width="8.796875" style="5"/>
+    <col min="3" max="7" width="8.796875" style="3"/>
+    <col min="8" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
         <v>18</v>
       </c>
@@ -2489,7 +3209,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="8">
         <v>91</v>
       </c>
@@ -2512,7 +3232,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="8">
         <v>92</v>
       </c>
@@ -2535,7 +3255,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="8">
         <v>93</v>
       </c>
@@ -2558,7 +3278,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="8">
         <v>94</v>
       </c>
@@ -2581,7 +3301,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="8">
         <v>95</v>
       </c>
@@ -2604,7 +3324,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="8">
         <v>96</v>
       </c>
@@ -2627,7 +3347,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="8">
         <v>97</v>
       </c>
@@ -2650,7 +3370,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="8">
         <v>98</v>
       </c>
@@ -2673,7 +3393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="8">
         <v>99</v>
       </c>
@@ -2696,7 +3416,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="8">
         <v>100</v>
       </c>
